--- a/Master Lists.xlsx
+++ b/Master Lists.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Item Master" sheetId="1" r:id="rId1"/>
@@ -1492,10 +1492,19 @@
     <t>DI</t>
   </si>
   <si>
+    <t>MRI Handicap Toilet</t>
+  </si>
+  <si>
+    <t>IR Handicap Toilet</t>
+  </si>
+  <si>
+    <t>X-Ray Handicap Toilet</t>
+  </si>
+  <si>
+    <t>AMU</t>
+  </si>
+  <si>
     <t>Handicap Toilet</t>
-  </si>
-  <si>
-    <t>AMU</t>
   </si>
   <si>
     <t>KU</t>
@@ -16552,13 +16561,13 @@
         <v>486</v>
       </c>
       <c r="B189" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C189" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D189" s="1" t="s">
         <v>489</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>488</v>
       </c>
       <c r="E189" s="1">
         <v>188</v>
@@ -16593,13 +16602,13 @@
         <v>486</v>
       </c>
       <c r="B190" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C190" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D190" s="1" t="s">
         <v>490</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>488</v>
       </c>
       <c r="E190" s="1">
         <v>189</v>
@@ -16634,13 +16643,13 @@
         <v>486</v>
       </c>
       <c r="B191" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>491</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="E191" s="1">
         <v>190</v>
@@ -16675,13 +16684,13 @@
         <v>486</v>
       </c>
       <c r="B192" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C192" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="D192" s="1" t="s">
         <v>492</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>488</v>
       </c>
       <c r="E192" s="1">
         <v>191</v>
@@ -16716,13 +16725,13 @@
         <v>486</v>
       </c>
       <c r="B193" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E193" s="1">
         <v>192</v>
@@ -16740,10 +16749,10 @@
         <v>14</v>
       </c>
       <c r="J193" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K193" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L193" s="2" t="s">
         <v>14</v>
@@ -16757,13 +16766,13 @@
         <v>486</v>
       </c>
       <c r="B194" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E194" s="1">
         <v>193</v>
@@ -16781,10 +16790,10 @@
         <v>14</v>
       </c>
       <c r="J194" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K194" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L194" s="2" t="s">
         <v>14</v>
@@ -16801,10 +16810,10 @@
         <v>5</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E195" s="1">
         <v>194</v>
@@ -16842,10 +16851,10 @@
         <v>5</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E196" s="1">
         <v>195</v>
@@ -16883,10 +16892,10 @@
         <v>5</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E197" s="1">
         <v>196</v>
@@ -16924,10 +16933,10 @@
         <v>5</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E198" s="1">
         <v>197</v>
@@ -16965,10 +16974,10 @@
         <v>5</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E199" s="1">
         <v>198</v>
@@ -17006,7 +17015,7 @@
         <v>5</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>502</v>
@@ -17047,7 +17056,7 @@
         <v>5</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="D201" s="1" t="s">
         <v>503</v>
@@ -17088,10 +17097,10 @@
         <v>5</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E202" s="1">
         <v>201</v>
@@ -17129,10 +17138,10 @@
         <v>5</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E203" s="1">
         <v>202</v>
@@ -17167,13 +17176,13 @@
         <v>486</v>
       </c>
       <c r="B204" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="E204" s="1">
         <v>203</v>
@@ -17208,13 +17217,13 @@
         <v>486</v>
       </c>
       <c r="B205" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="E205" s="1">
         <v>204</v>
@@ -17252,10 +17261,10 @@
         <v>6</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E206" s="1">
         <v>205</v>
@@ -17293,10 +17302,10 @@
         <v>6</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E207" s="1">
         <v>206</v>
@@ -17334,10 +17343,10 @@
         <v>6</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E208" s="1">
         <v>207</v>
@@ -17375,10 +17384,10 @@
         <v>6</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E209" s="1">
         <v>208</v>
@@ -17416,10 +17425,10 @@
         <v>6</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E210" s="1">
         <v>209</v>
@@ -17457,7 +17466,7 @@
         <v>6</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D211" s="1" t="s">
         <v>502</v>
@@ -17498,7 +17507,7 @@
         <v>6</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D212" s="1" t="s">
         <v>503</v>
@@ -17539,10 +17548,10 @@
         <v>6</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E213" s="1">
         <v>212</v>
@@ -17580,10 +17589,10 @@
         <v>6</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E214" s="1">
         <v>213</v>
@@ -17618,13 +17627,13 @@
         <v>486</v>
       </c>
       <c r="B215" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="E215" s="1">
         <v>214</v>
@@ -17659,13 +17668,13 @@
         <v>486</v>
       </c>
       <c r="B216" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C216" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="D216" s="1" t="s">
         <v>508</v>
-      </c>
-      <c r="D216" s="1" t="s">
-        <v>495</v>
       </c>
       <c r="E216" s="1">
         <v>215</v>
@@ -17703,10 +17712,10 @@
         <v>7</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E217" s="1">
         <v>216</v>
@@ -17744,10 +17753,10 @@
         <v>7</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E218" s="1">
         <v>217</v>
@@ -17785,10 +17794,10 @@
         <v>7</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E219" s="1">
         <v>218</v>
@@ -17826,10 +17835,10 @@
         <v>7</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E220" s="1">
         <v>219</v>
@@ -17867,10 +17876,10 @@
         <v>7</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E221" s="1">
         <v>220</v>
@@ -17908,7 +17917,7 @@
         <v>7</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="D222" s="1" t="s">
         <v>502</v>
@@ -17949,7 +17958,7 @@
         <v>7</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="D223" s="1" t="s">
         <v>503</v>
@@ -17990,10 +17999,10 @@
         <v>7</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E224" s="1">
         <v>223</v>
@@ -18031,10 +18040,10 @@
         <v>7</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E225" s="1">
         <v>224</v>
@@ -18069,13 +18078,13 @@
         <v>486</v>
       </c>
       <c r="B226" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="E226" s="1">
         <v>225</v>
@@ -18110,13 +18119,13 @@
         <v>486</v>
       </c>
       <c r="B227" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="E227" s="1">
         <v>226</v>
@@ -18154,10 +18163,10 @@
         <v>8</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E228" s="1">
         <v>227</v>
@@ -18195,10 +18204,10 @@
         <v>8</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E229" s="1">
         <v>228</v>
@@ -18236,10 +18245,10 @@
         <v>8</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E230" s="1">
         <v>229</v>
@@ -18277,10 +18286,10 @@
         <v>8</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E231" s="1">
         <v>230</v>
@@ -18318,10 +18327,10 @@
         <v>8</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E232" s="1">
         <v>231</v>
@@ -18359,7 +18368,7 @@
         <v>8</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>502</v>
@@ -18400,7 +18409,7 @@
         <v>8</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D234" s="1" t="s">
         <v>503</v>
@@ -18441,10 +18450,10 @@
         <v>8</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E235" s="1">
         <v>234</v>
@@ -18482,10 +18491,10 @@
         <v>8</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E236" s="1">
         <v>235</v>
@@ -18520,13 +18529,13 @@
         <v>486</v>
       </c>
       <c r="B237" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="E237" s="1">
         <v>236</v>
@@ -18561,13 +18570,13 @@
         <v>486</v>
       </c>
       <c r="B238" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="E238" s="1">
         <v>237</v>
@@ -18605,10 +18614,10 @@
         <v>9</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E239" s="1">
         <v>238</v>
@@ -18646,10 +18655,10 @@
         <v>9</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E240" s="1">
         <v>239</v>
@@ -18687,10 +18696,10 @@
         <v>9</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E241" s="1">
         <v>240</v>
@@ -18728,10 +18737,10 @@
         <v>9</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E242" s="1">
         <v>241</v>
@@ -18769,10 +18778,10 @@
         <v>9</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E243" s="1">
         <v>242</v>
@@ -18810,7 +18819,7 @@
         <v>9</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D244" s="1" t="s">
         <v>502</v>
@@ -18851,7 +18860,7 @@
         <v>9</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D245" s="1" t="s">
         <v>503</v>
@@ -18892,10 +18901,10 @@
         <v>9</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E246" s="1">
         <v>245</v>
@@ -18933,10 +18942,10 @@
         <v>9</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E247" s="1">
         <v>246</v>
@@ -18971,13 +18980,13 @@
         <v>486</v>
       </c>
       <c r="B248" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="E248" s="1">
         <v>247</v>
@@ -19012,13 +19021,13 @@
         <v>486</v>
       </c>
       <c r="B249" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="E249" s="1">
         <v>248</v>
@@ -19056,10 +19065,10 @@
         <v>10</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E250" s="1">
         <v>249</v>
@@ -19097,10 +19106,10 @@
         <v>10</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E251" s="1">
         <v>250</v>
@@ -19138,10 +19147,10 @@
         <v>10</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E252" s="1">
         <v>251</v>
@@ -19179,10 +19188,10 @@
         <v>10</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E253" s="1">
         <v>252</v>
@@ -19220,10 +19229,10 @@
         <v>10</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E254" s="1">
         <v>253</v>
@@ -19261,7 +19270,7 @@
         <v>10</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D255" s="1" t="s">
         <v>502</v>
@@ -19302,7 +19311,7 @@
         <v>10</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D256" s="1" t="s">
         <v>503</v>
@@ -19343,10 +19352,10 @@
         <v>10</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E257" s="1">
         <v>256</v>
@@ -19384,10 +19393,10 @@
         <v>10</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E258" s="1">
         <v>257</v>
@@ -19422,13 +19431,13 @@
         <v>486</v>
       </c>
       <c r="B259" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="E259" s="1">
         <v>258</v>
@@ -19449,10 +19458,10 @@
         <v>14</v>
       </c>
       <c r="K259" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L259" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M259" s="2" t="s">
         <v>14</v>
@@ -19463,13 +19472,13 @@
         <v>486</v>
       </c>
       <c r="B260" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="E260" s="1">
         <v>259</v>
@@ -19490,10 +19499,10 @@
         <v>14</v>
       </c>
       <c r="K260" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L260" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M260" s="2" t="s">
         <v>14</v>
@@ -19507,10 +19516,10 @@
         <v>11</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E261" s="1">
         <v>260</v>
@@ -19548,10 +19557,10 @@
         <v>11</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E262" s="1">
         <v>261</v>
@@ -19589,10 +19598,10 @@
         <v>11</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E263" s="1">
         <v>262</v>
@@ -19630,10 +19639,10 @@
         <v>11</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E264" s="1">
         <v>263</v>
@@ -19671,10 +19680,10 @@
         <v>11</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E265" s="1">
         <v>264</v>
@@ -19709,13 +19718,13 @@
         <v>486</v>
       </c>
       <c r="B266" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="E266" s="1">
         <v>265</v>
@@ -19750,13 +19759,13 @@
         <v>486</v>
       </c>
       <c r="B267" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="E267" s="1">
         <v>266</v>
@@ -19794,10 +19803,10 @@
         <v>12</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E268" s="1">
         <v>267</v>
@@ -19835,10 +19844,10 @@
         <v>12</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E269" s="1">
         <v>268</v>
@@ -19876,10 +19885,10 @@
         <v>12</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E270" s="1">
         <v>269</v>
@@ -19917,10 +19926,10 @@
         <v>12</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E271" s="1">
         <v>270</v>
@@ -19958,10 +19967,10 @@
         <v>12</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E272" s="1">
         <v>271</v>
@@ -19996,13 +20005,13 @@
         <v>486</v>
       </c>
       <c r="B273" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="E273" s="1">
         <v>272</v>
@@ -20037,13 +20046,13 @@
         <v>486</v>
       </c>
       <c r="B274" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="E274" s="1">
         <v>273</v>
@@ -20081,10 +20090,10 @@
         <v>13</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E275" s="1">
         <v>274</v>
@@ -20122,10 +20131,10 @@
         <v>13</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E276" s="1">
         <v>275</v>
@@ -20163,10 +20172,10 @@
         <v>13</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E277" s="1">
         <v>276</v>
@@ -20204,10 +20213,10 @@
         <v>13</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E278" s="1">
         <v>277</v>
@@ -20245,10 +20254,10 @@
         <v>13</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E279" s="1">
         <v>278</v>
@@ -20283,13 +20292,13 @@
         <v>486</v>
       </c>
       <c r="B280" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="E280" s="1">
         <v>279</v>
@@ -20324,13 +20333,13 @@
         <v>486</v>
       </c>
       <c r="B281" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="E281" s="1">
         <v>280</v>
@@ -20368,10 +20377,10 @@
         <v>14</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E282" s="1">
         <v>281</v>
@@ -20409,10 +20418,10 @@
         <v>14</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E283" s="1">
         <v>282</v>
@@ -20450,10 +20459,10 @@
         <v>14</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E284" s="1">
         <v>283</v>
@@ -20491,10 +20500,10 @@
         <v>14</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E285" s="1">
         <v>284</v>
@@ -20532,10 +20541,10 @@
         <v>14</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E286" s="1">
         <v>285</v>
@@ -20570,13 +20579,13 @@
         <v>486</v>
       </c>
       <c r="B287" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="E287" s="1">
         <v>286</v>
@@ -20611,13 +20620,13 @@
         <v>486</v>
       </c>
       <c r="B288" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="E288" s="1">
         <v>287</v>
@@ -20655,10 +20664,10 @@
         <v>15</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E289" s="1">
         <v>288</v>
@@ -20696,10 +20705,10 @@
         <v>15</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E290" s="1">
         <v>289</v>
@@ -20737,10 +20746,10 @@
         <v>15</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E291" s="1">
         <v>290</v>
@@ -20778,10 +20787,10 @@
         <v>15</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E292" s="1">
         <v>291</v>
@@ -20819,10 +20828,10 @@
         <v>15</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E293" s="1">
         <v>292</v>
@@ -20857,13 +20866,13 @@
         <v>486</v>
       </c>
       <c r="B294" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="E294" s="1">
         <v>293</v>
@@ -20898,13 +20907,13 @@
         <v>486</v>
       </c>
       <c r="B295" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="E295" s="1">
         <v>294</v>
@@ -20942,10 +20951,10 @@
         <v>16</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E296" s="1">
         <v>295</v>
@@ -20983,10 +20992,10 @@
         <v>16</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E297" s="1">
         <v>296</v>
@@ -21024,10 +21033,10 @@
         <v>16</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E298" s="1">
         <v>297</v>
@@ -21065,10 +21074,10 @@
         <v>16</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E299" s="1">
         <v>298</v>
@@ -21106,10 +21115,10 @@
         <v>16</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E300" s="1">
         <v>299</v>
@@ -21141,16 +21150,16 @@
     </row>
     <row r="301">
       <c r="A301" s="1" t="s">
-        <v>522</v>
+        <v>486</v>
       </c>
       <c r="B301" s="1">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>524</v>
+        <v>502</v>
       </c>
       <c r="E301" s="1">
         <v>300</v>
@@ -21174,24 +21183,24 @@
         <v>14</v>
       </c>
       <c r="L301" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M301" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="s">
-        <v>522</v>
+        <v>486</v>
       </c>
       <c r="B302" s="1">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>525</v>
+        <v>503</v>
       </c>
       <c r="E302" s="1">
         <v>301</v>
@@ -21215,24 +21224,24 @@
         <v>14</v>
       </c>
       <c r="L302" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M302" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B303" s="1">
         <v>1</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E303" s="1">
         <v>302</v>
@@ -21264,16 +21273,16 @@
     </row>
     <row r="304">
       <c r="A304" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B304" s="1">
         <v>1</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E304" s="1">
         <v>303</v>
@@ -21305,16 +21314,16 @@
     </row>
     <row r="305">
       <c r="A305" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B305" s="1">
         <v>1</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E305" s="1">
         <v>304</v>
@@ -21346,16 +21355,16 @@
     </row>
     <row r="306">
       <c r="A306" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B306" s="1">
         <v>1</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E306" s="1">
         <v>305</v>
@@ -21387,16 +21396,16 @@
     </row>
     <row r="307">
       <c r="A307" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B307" s="1">
         <v>1</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E307" s="1">
         <v>306</v>
@@ -21428,16 +21437,16 @@
     </row>
     <row r="308">
       <c r="A308" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B308" s="1">
         <v>1</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E308" s="1">
         <v>307</v>
@@ -21469,16 +21478,16 @@
     </row>
     <row r="309">
       <c r="A309" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B309" s="1">
         <v>1</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E309" s="1">
         <v>308</v>
@@ -21510,16 +21519,16 @@
     </row>
     <row r="310">
       <c r="A310" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B310" s="1">
         <v>1</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E310" s="1">
         <v>309</v>
@@ -21551,16 +21560,16 @@
     </row>
     <row r="311">
       <c r="A311" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B311" s="1">
         <v>1</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E311" s="1">
         <v>310</v>
@@ -21592,16 +21601,16 @@
     </row>
     <row r="312">
       <c r="A312" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B312" s="1">
         <v>1</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E312" s="1">
         <v>311</v>
@@ -21633,16 +21642,16 @@
     </row>
     <row r="313">
       <c r="A313" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B313" s="1">
         <v>1</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E313" s="1">
         <v>312</v>
@@ -21674,16 +21683,16 @@
     </row>
     <row r="314">
       <c r="A314" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B314" s="1">
         <v>1</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E314" s="1">
         <v>313</v>
@@ -21715,16 +21724,16 @@
     </row>
     <row r="315">
       <c r="A315" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B315" s="1">
         <v>1</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E315" s="1">
         <v>314</v>
@@ -21756,16 +21765,16 @@
     </row>
     <row r="316">
       <c r="A316" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B316" s="1">
         <v>1</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E316" s="1">
         <v>315</v>
@@ -21797,16 +21806,16 @@
     </row>
     <row r="317">
       <c r="A317" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B317" s="1">
         <v>1</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E317" s="1">
         <v>316</v>
@@ -21838,16 +21847,16 @@
     </row>
     <row r="318">
       <c r="A318" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B318" s="1">
         <v>1</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E318" s="1">
         <v>317</v>
@@ -21874,6 +21883,88 @@
         <v>14</v>
       </c>
       <c r="M318" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="B319" s="1">
+        <v>1</v>
+      </c>
+      <c r="C319" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D319" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="E319" s="1">
+        <v>318</v>
+      </c>
+      <c r="F319" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G319" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H319" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I319" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J319" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K319" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L319" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M319" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="B320" s="1">
+        <v>1</v>
+      </c>
+      <c r="C320" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="E320" s="1">
+        <v>319</v>
+      </c>
+      <c r="F320" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G320" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H320" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I320" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J320" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K320" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L320" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M320" s="2" t="s">
         <v>15</v>
       </c>
     </row>
@@ -21894,28 +21985,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>174</v>
@@ -21923,16 +22014,16 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -21946,16 +22037,16 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="E3" s="1">
         <v>2</v>
@@ -21964,7 +22055,7 @@
         <v>15</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="H3" s="1">
         <v>8</v>
@@ -21975,16 +22066,16 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="E4" s="1">
         <v>3</v>
@@ -21993,7 +22084,7 @@
         <v>15</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="H4" s="1">
         <v>7</v>
@@ -22004,16 +22095,16 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="E5" s="1">
         <v>4</v>
@@ -22022,7 +22113,7 @@
         <v>15</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="H5" s="1">
         <v>11</v>
@@ -22033,16 +22124,16 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="E6" s="1">
         <v>5</v>
@@ -22056,16 +22147,16 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
@@ -22074,7 +22165,7 @@
         <v>15</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="H7" s="1">
         <v>9</v>
@@ -22085,16 +22176,16 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E8" s="1">
         <v>7</v>
@@ -22108,16 +22199,16 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E9" s="1">
         <v>8</v>
@@ -22126,7 +22217,7 @@
         <v>15</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="H9" s="1">
         <v>17</v>
@@ -22137,16 +22228,16 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>569</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>566</v>
       </c>
       <c r="E10" s="1">
         <v>9</v>
@@ -22155,7 +22246,7 @@
         <v>15</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="H10" s="1">
         <v>16</v>
@@ -22166,16 +22257,16 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E11" s="1">
         <v>10</v>
@@ -22184,7 +22275,7 @@
         <v>15</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>15</v>
@@ -22192,10 +22283,10 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>14</v>
@@ -22204,7 +22295,7 @@
         <v>15</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="H12" s="1">
         <v>1</v>
@@ -22212,10 +22303,10 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>14</v>
@@ -22224,7 +22315,7 @@
         <v>15</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="H13" s="1">
         <v>2</v>
@@ -22235,10 +22326,10 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>14</v>
@@ -22247,7 +22338,7 @@
         <v>15</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="H14" s="1">
         <v>3</v>
@@ -22258,10 +22349,10 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>14</v>
@@ -22270,7 +22361,7 @@
         <v>15</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="H15" s="1">
         <v>4</v>
@@ -22281,10 +22372,10 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>14</v>
@@ -22293,7 +22384,7 @@
         <v>15</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="H16" s="1">
         <v>5</v>
@@ -22304,10 +22395,10 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>14</v>
@@ -22316,7 +22407,7 @@
         <v>15</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="H17" s="1">
         <v>6</v>
@@ -22327,10 +22418,10 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>14</v>
@@ -22339,7 +22430,7 @@
         <v>15</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="H18" s="1">
         <v>10</v>
@@ -22350,10 +22441,10 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>14</v>
@@ -22362,7 +22453,7 @@
         <v>15</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="H19" s="1">
         <v>12</v>
@@ -22373,10 +22464,10 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>14</v>
@@ -22385,7 +22476,7 @@
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="H20" s="1">
         <v>13</v>
@@ -22396,10 +22487,10 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>14</v>
@@ -22408,7 +22499,7 @@
         <v>15</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="H21" s="1">
         <v>14</v>
@@ -22419,10 +22510,10 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>14</v>
@@ -22431,7 +22522,7 @@
         <v>15</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="H22" s="1">
         <v>15</v>
@@ -22442,10 +22533,10 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>14</v>
@@ -22454,7 +22545,7 @@
         <v>15</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="H23" s="1">
         <v>18</v>

--- a/Master Lists.xlsx
+++ b/Master Lists.xlsx
@@ -3558,7 +3558,7 @@
         <v>14</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>15</v>

--- a/Master Lists.xlsx
+++ b/Master Lists.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Item Master" sheetId="1" r:id="rId1"/>
@@ -7404,6 +7404,32 @@
         <v>15</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>166</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D64" s="1">
+        <v>63</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G64" s="4">
+        <v>78.480000000000004</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -7979,6 +8005,14 @@
     <row r="72">
       <c r="B72" s="3" t="s">
         <v>259</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>166</v>
+      </c>
+      <c r="B73" t="s">
+        <v>166</v>
       </c>
     </row>
   </sheetData>

--- a/Master Lists.xlsx
+++ b/Master Lists.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4" activeTab="2"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Item Master" sheetId="1" r:id="rId1"/>
@@ -838,7 +838,7 @@
     <t>A1-3</t>
   </si>
   <si>
-    <t>A4-7</t>
+    <t>A4-8</t>
   </si>
   <si>
     <t>B1-4</t>
@@ -968,9 +968,6 @@
   </si>
   <si>
     <t>abxk2928</t>
-  </si>
-  <si>
-    <t>A4-8</t>
   </si>
   <si>
     <t>Mohammad Johan Bin Hamzah</t>
@@ -8381,7 +8378,7 @@
         <v>299</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>314</v>
+        <v>270</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>15</v>
@@ -8389,19 +8386,19 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>317</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>299</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>314</v>
+        <v>270</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>15</v>
@@ -8409,13 +8406,13 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>320</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>299</v>
@@ -8429,13 +8426,13 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>323</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>299</v>
@@ -8449,13 +8446,13 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>326</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>299</v>
@@ -8469,13 +8466,13 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>329</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>299</v>
@@ -8489,13 +8486,13 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>332</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>299</v>
@@ -8509,13 +8506,13 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>335</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>299</v>
@@ -8529,13 +8526,13 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>338</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>299</v>
@@ -8549,13 +8546,13 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>341</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>299</v>
@@ -8569,13 +8566,13 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>344</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>299</v>
@@ -8589,13 +8586,13 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>347</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>299</v>
@@ -8609,13 +8606,13 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>350</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>299</v>
@@ -8629,13 +8626,13 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>353</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>299</v>
@@ -8649,13 +8646,13 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>356</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>299</v>
@@ -8669,13 +8666,13 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>359</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>299</v>
@@ -8689,13 +8686,13 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="1" t="s">
         <v>361</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>362</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>299</v>
@@ -8709,13 +8706,13 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>365</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>299</v>
@@ -8743,10 +8740,10 @@
   <sheetData>
     <row r="1" ht="15">
       <c r="A1" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>366</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>367</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>299</v>
@@ -8763,10 +8760,10 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>369</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>15</v>
@@ -8783,13 +8780,13 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>371</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>14</v>
@@ -8803,10 +8800,10 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>373</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>14</v>
@@ -8823,10 +8820,10 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>375</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>14</v>
@@ -8846,7 +8843,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>14</v>
@@ -8863,10 +8860,10 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>377</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>14</v>
@@ -8883,10 +8880,10 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
@@ -8919,16 +8916,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>382</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -8937,39 +8934,39 @@
         <v>175</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>388</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>392</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -9001,16 +8998,16 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E3" s="1">
         <v>2</v>
@@ -9042,16 +9039,16 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E4" s="1">
         <v>3</v>
@@ -9083,16 +9080,16 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E5" s="1">
         <v>4</v>
@@ -9124,16 +9121,16 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E6" s="1">
         <v>5</v>
@@ -9165,16 +9162,16 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
@@ -9206,16 +9203,16 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E8" s="1">
         <v>7</v>
@@ -9247,16 +9244,16 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E9" s="1">
         <v>8</v>
@@ -9288,16 +9285,16 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E10" s="1">
         <v>9</v>
@@ -9329,16 +9326,16 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E11" s="1">
         <v>10</v>
@@ -9370,16 +9367,16 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E12" s="1">
         <v>11</v>
@@ -9411,16 +9408,16 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B13" s="1">
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E13" s="1">
         <v>12</v>
@@ -9452,16 +9449,16 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B14" s="1">
         <v>2</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>404</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>405</v>
       </c>
       <c r="E14" s="1">
         <v>13</v>
@@ -9493,16 +9490,16 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B15" s="1">
         <v>2</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E15" s="1">
         <v>14</v>
@@ -9534,16 +9531,16 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B16" s="1">
         <v>2</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E16" s="1">
         <v>15</v>
@@ -9575,16 +9572,16 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B17" s="1">
         <v>2</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>408</v>
       </c>
       <c r="E17" s="1">
         <v>16</v>
@@ -9616,16 +9613,16 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B18" s="1">
         <v>2</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E18" s="1">
         <v>17</v>
@@ -9657,16 +9654,16 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B19" s="1">
         <v>2</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E19" s="1">
         <v>18</v>
@@ -9698,16 +9695,16 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B20" s="1">
         <v>2</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E20" s="1">
         <v>19</v>
@@ -9739,16 +9736,16 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B21" s="1">
         <v>2</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>412</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>413</v>
       </c>
       <c r="E21" s="1">
         <v>20</v>
@@ -9780,16 +9777,16 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B22" s="1">
         <v>2</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E22" s="1">
         <v>21</v>
@@ -9821,16 +9818,16 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B23" s="1">
         <v>2</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E23" s="1">
         <v>22</v>
@@ -9862,16 +9859,16 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B24" s="1">
         <v>2</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E24" s="1">
         <v>23</v>
@@ -9903,16 +9900,16 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B25" s="1">
         <v>2</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E25" s="1">
         <v>24</v>
@@ -9944,16 +9941,16 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B26" s="1">
         <v>2</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E26" s="1">
         <v>25</v>
@@ -9985,16 +9982,16 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B27" s="1">
         <v>2</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E27" s="1">
         <v>26</v>
@@ -10026,16 +10023,16 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B28" s="1">
         <v>2</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E28" s="1">
         <v>27</v>
@@ -10067,16 +10064,16 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B29" s="1">
         <v>2</v>
       </c>
       <c r="C29" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>421</v>
       </c>
       <c r="E29" s="1">
         <v>28</v>
@@ -10108,16 +10105,16 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B30" s="1">
         <v>2</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E30" s="1">
         <v>29</v>
@@ -10149,16 +10146,16 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B31" s="1">
         <v>2</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E31" s="1">
         <v>30</v>
@@ -10190,16 +10187,16 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B32" s="1">
         <v>3</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>423</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>424</v>
       </c>
       <c r="E32" s="1">
         <v>31</v>
@@ -10231,16 +10228,16 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B33" s="1">
         <v>3</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E33" s="1">
         <v>32</v>
@@ -10272,16 +10269,16 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B34" s="1">
         <v>3</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E34" s="1">
         <v>33</v>
@@ -10313,16 +10310,16 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B35" s="1">
         <v>3</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E35" s="1">
         <v>34</v>
@@ -10354,16 +10351,16 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B36" s="1">
         <v>3</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E36" s="1">
         <v>35</v>
@@ -10395,16 +10392,16 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B37" s="1">
         <v>3</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E37" s="1">
         <v>36</v>
@@ -10436,16 +10433,16 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B38" s="1">
         <v>3</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E38" s="1">
         <v>37</v>
@@ -10477,16 +10474,16 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B39" s="1">
         <v>3</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E39" s="1">
         <v>38</v>
@@ -10518,16 +10515,16 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B40" s="1">
         <v>3</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E40" s="1">
         <v>39</v>
@@ -10559,16 +10556,16 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B41" s="1">
         <v>3</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E41" s="1">
         <v>40</v>
@@ -10600,16 +10597,16 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B42" s="1">
         <v>3</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E42" s="1">
         <v>41</v>
@@ -10641,16 +10638,16 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B43" s="1">
         <v>3</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E43" s="1">
         <v>42</v>
@@ -10682,16 +10679,16 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B44" s="1">
         <v>3</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E44" s="1">
         <v>43</v>
@@ -10723,16 +10720,16 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B45" s="1">
         <v>3</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E45" s="1">
         <v>44</v>
@@ -10764,16 +10761,16 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B46" s="1">
         <v>3</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E46" s="1">
         <v>45</v>
@@ -10805,16 +10802,16 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B47" s="1">
         <v>3</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E47" s="1">
         <v>46</v>
@@ -10846,16 +10843,16 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B48" s="1">
         <v>3</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E48" s="1">
         <v>47</v>
@@ -10887,16 +10884,16 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B49" s="1">
         <v>3</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E49" s="1">
         <v>48</v>
@@ -10928,16 +10925,16 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B50" s="1">
         <v>3</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E50" s="1">
         <v>49</v>
@@ -10969,16 +10966,16 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B51" s="1">
         <v>3</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E51" s="1">
         <v>50</v>
@@ -11010,16 +11007,16 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B52" s="1">
         <v>3</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E52" s="1">
         <v>51</v>
@@ -11051,16 +11048,16 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B53" s="1">
         <v>3</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E53" s="1">
         <v>52</v>
@@ -11092,16 +11089,16 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B54" s="1">
         <v>3</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E54" s="1">
         <v>53</v>
@@ -11133,16 +11130,16 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B55" s="1">
         <v>3</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E55" s="1">
         <v>54</v>
@@ -11174,16 +11171,16 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B56" s="1">
         <v>3</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E56" s="1">
         <v>55</v>
@@ -11215,16 +11212,16 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B57" s="1">
         <v>3</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E57" s="1">
         <v>56</v>
@@ -11256,16 +11253,16 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B58" s="1">
         <v>3</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E58" s="1">
         <v>57</v>
@@ -11297,16 +11294,16 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B59" s="1">
         <v>3</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E59" s="1">
         <v>58</v>
@@ -11338,16 +11335,16 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B60" s="1">
         <v>3</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E60" s="1">
         <v>59</v>
@@ -11379,16 +11376,16 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B61" s="1">
         <v>3</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E61" s="1">
         <v>60</v>
@@ -11420,16 +11417,16 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B62" s="1">
         <v>3</v>
       </c>
       <c r="C62" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>423</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>424</v>
       </c>
       <c r="E62" s="1">
         <v>61</v>
@@ -11461,16 +11458,16 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B63" s="1">
         <v>3</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E63" s="1">
         <v>62</v>
@@ -11502,16 +11499,16 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B64" s="1">
         <v>3</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E64" s="1">
         <v>63</v>
@@ -11543,16 +11540,16 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B65" s="1">
         <v>3</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E65" s="1">
         <v>64</v>
@@ -11584,16 +11581,16 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B66" s="1">
         <v>3</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E66" s="1">
         <v>65</v>
@@ -11625,16 +11622,16 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B67" s="1">
         <v>4</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E67" s="1">
         <v>66</v>
@@ -11666,16 +11663,16 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B68" s="1">
         <v>4</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E68" s="1">
         <v>67</v>
@@ -11707,16 +11704,16 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B69" s="1">
         <v>4</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E69" s="1">
         <v>68</v>
@@ -11748,16 +11745,16 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B70" s="1">
         <v>4</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E70" s="1">
         <v>69</v>
@@ -11789,16 +11786,16 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B71" s="1">
         <v>4</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E71" s="1">
         <v>70</v>
@@ -11830,16 +11827,16 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B72" s="1">
         <v>4</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E72" s="1">
         <v>71</v>
@@ -11871,16 +11868,16 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B73" s="1">
         <v>4</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E73" s="1">
         <v>72</v>
@@ -11912,16 +11909,16 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B74" s="1">
         <v>4</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E74" s="1">
         <v>73</v>
@@ -11953,16 +11950,16 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B75" s="1">
         <v>4</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E75" s="1">
         <v>74</v>
@@ -11994,16 +11991,16 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B76" s="1">
         <v>4</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E76" s="1">
         <v>75</v>
@@ -12035,16 +12032,16 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B77" s="1">
         <v>4</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E77" s="1">
         <v>76</v>
@@ -12076,16 +12073,16 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B78" s="1">
         <v>4</v>
       </c>
       <c r="C78" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>453</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>454</v>
       </c>
       <c r="E78" s="1">
         <v>77</v>
@@ -12117,16 +12114,16 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B79" s="1">
         <v>4</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E79" s="1">
         <v>78</v>
@@ -12158,16 +12155,16 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B80" s="1">
         <v>4</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E80" s="1">
         <v>79</v>
@@ -12199,16 +12196,16 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B81" s="1">
         <v>4</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E81" s="1">
         <v>80</v>
@@ -12240,16 +12237,16 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B82" s="1">
         <v>4</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E82" s="1">
         <v>81</v>
@@ -12281,16 +12278,16 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B83" s="1">
         <v>4</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E83" s="1">
         <v>82</v>
@@ -12322,16 +12319,16 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B84" s="1">
         <v>4</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E84" s="1">
         <v>83</v>
@@ -12363,16 +12360,16 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B85" s="1">
         <v>4</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E85" s="1">
         <v>84</v>
@@ -12404,16 +12401,16 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B86" s="1">
         <v>4</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E86" s="1">
         <v>85</v>
@@ -12445,16 +12442,16 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B87" s="1">
         <v>4</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E87" s="1">
         <v>86</v>
@@ -12486,16 +12483,16 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B88" s="1">
         <v>4</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E88" s="1">
         <v>87</v>
@@ -12527,16 +12524,16 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B89" s="1">
         <v>4</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E89" s="1">
         <v>88</v>
@@ -12568,16 +12565,16 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B90" s="1">
         <v>4</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E90" s="1">
         <v>89</v>
@@ -12609,16 +12606,16 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B91" s="1">
         <v>4</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E91" s="1">
         <v>90</v>
@@ -12650,16 +12647,16 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B92" s="1">
         <v>4</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E92" s="1">
         <v>91</v>
@@ -12691,16 +12688,16 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B93" s="1">
         <v>4</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E93" s="1">
         <v>92</v>
@@ -12732,16 +12729,16 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B94" s="1">
         <v>4</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E94" s="1">
         <v>93</v>
@@ -12773,16 +12770,16 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B95" s="1">
         <v>4</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E95" s="1">
         <v>94</v>
@@ -12814,16 +12811,16 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B96" s="1">
         <v>4</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E96" s="1">
         <v>95</v>
@@ -12855,16 +12852,16 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B97" s="1">
         <v>4</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E97" s="1">
         <v>96</v>
@@ -12896,16 +12893,16 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B98" s="1">
         <v>4</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E98" s="1">
         <v>97</v>
@@ -12937,16 +12934,16 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B99" s="1">
         <v>4</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E99" s="1">
         <v>98</v>
@@ -12978,16 +12975,16 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B100" s="1">
         <v>4</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E100" s="1">
         <v>99</v>
@@ -13019,16 +13016,16 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B101" s="1">
         <v>4</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E101" s="1">
         <v>100</v>
@@ -13060,16 +13057,16 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B102" s="1">
         <v>4</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E102" s="1">
         <v>101</v>
@@ -13101,16 +13098,16 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B103" s="1">
         <v>4</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E103" s="1">
         <v>102</v>
@@ -13142,16 +13139,16 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B104" s="1">
         <v>5</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E104" s="1">
         <v>103</v>
@@ -13183,16 +13180,16 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B105" s="1">
         <v>5</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E105" s="1">
         <v>104</v>
@@ -13224,16 +13221,16 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B106" s="1">
         <v>5</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E106" s="1">
         <v>105</v>
@@ -13265,16 +13262,16 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B107" s="1">
         <v>5</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E107" s="1">
         <v>106</v>
@@ -13306,16 +13303,16 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B108" s="1">
         <v>5</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E108" s="1">
         <v>107</v>
@@ -13347,16 +13344,16 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B109" s="1">
         <v>5</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E109" s="1">
         <v>108</v>
@@ -13388,16 +13385,16 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B110" s="1">
         <v>5</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E110" s="1">
         <v>109</v>
@@ -13429,16 +13426,16 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B111" s="1">
         <v>5</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E111" s="1">
         <v>110</v>
@@ -13470,16 +13467,16 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B112" s="1">
         <v>5</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E112" s="1">
         <v>111</v>
@@ -13511,16 +13508,16 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B113" s="1">
         <v>5</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E113" s="1">
         <v>112</v>
@@ -13552,16 +13549,16 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B114" s="1">
         <v>5</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E114" s="1">
         <v>113</v>
@@ -13593,16 +13590,16 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B115" s="1">
         <v>5</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E115" s="1">
         <v>114</v>
@@ -13634,16 +13631,16 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B116" s="1">
         <v>5</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E116" s="1">
         <v>115</v>
@@ -13675,16 +13672,16 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B117" s="1">
         <v>5</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E117" s="1">
         <v>116</v>
@@ -13716,16 +13713,16 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B118" s="1">
         <v>5</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E118" s="1">
         <v>117</v>
@@ -13757,16 +13754,16 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B119" s="1">
         <v>5</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E119" s="1">
         <v>118</v>
@@ -13798,16 +13795,16 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B120" s="1">
         <v>5</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E120" s="1">
         <v>119</v>
@@ -13839,16 +13836,16 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B121" s="1">
         <v>5</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E121" s="1">
         <v>120</v>
@@ -13880,16 +13877,16 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B122" s="1">
         <v>5</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E122" s="1">
         <v>121</v>
@@ -13921,16 +13918,16 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B123" s="1">
         <v>5</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E123" s="1">
         <v>122</v>
@@ -13962,16 +13959,16 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B124" s="1">
         <v>5</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E124" s="1">
         <v>123</v>
@@ -14003,16 +14000,16 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B125" s="1">
         <v>5</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E125" s="1">
         <v>124</v>
@@ -14044,16 +14041,16 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B126" s="1">
         <v>5</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E126" s="1">
         <v>125</v>
@@ -14085,16 +14082,16 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B127" s="1">
         <v>5</v>
       </c>
       <c r="C127" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>472</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>473</v>
       </c>
       <c r="E127" s="1">
         <v>126</v>
@@ -14126,16 +14123,16 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B128" s="1">
         <v>5</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E128" s="1">
         <v>127</v>
@@ -14167,16 +14164,16 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B129" s="1">
         <v>5</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E129" s="1">
         <v>128</v>
@@ -14208,16 +14205,16 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B130" s="1">
         <v>5</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E130" s="1">
         <v>129</v>
@@ -14249,16 +14246,16 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B131" s="1">
         <v>5</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E131" s="1">
         <v>130</v>
@@ -14290,16 +14287,16 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B132" s="1">
         <v>5</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E132" s="1">
         <v>131</v>
@@ -14331,16 +14328,16 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B133" s="1">
         <v>5</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E133" s="1">
         <v>132</v>
@@ -14372,16 +14369,16 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B134" s="1">
         <v>6</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E134" s="1">
         <v>133</v>
@@ -14413,16 +14410,16 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B135" s="1">
         <v>6</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E135" s="1">
         <v>134</v>
@@ -14454,16 +14451,16 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B136" s="1">
         <v>6</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E136" s="1">
         <v>135</v>
@@ -14495,16 +14492,16 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B137" s="1">
         <v>6</v>
       </c>
       <c r="C137" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>476</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>477</v>
       </c>
       <c r="E137" s="1">
         <v>136</v>
@@ -14536,16 +14533,16 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B138" s="1">
         <v>6</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E138" s="1">
         <v>137</v>
@@ -14577,16 +14574,16 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B139" s="1">
         <v>6</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E139" s="1">
         <v>138</v>
@@ -14618,16 +14615,16 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B140" s="1">
         <v>6</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E140" s="1">
         <v>139</v>
@@ -14659,16 +14656,16 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B141" s="1">
         <v>6</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E141" s="1">
         <v>140</v>
@@ -14700,16 +14697,16 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B142" s="1">
         <v>6</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E142" s="1">
         <v>141</v>
@@ -14741,16 +14738,16 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B143" s="1">
         <v>6</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E143" s="1">
         <v>142</v>
@@ -14782,16 +14779,16 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B144" s="1">
         <v>6</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E144" s="1">
         <v>143</v>
@@ -14823,16 +14820,16 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B145" s="1">
         <v>6</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E145" s="1">
         <v>144</v>
@@ -14864,16 +14861,16 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B146" s="1">
         <v>6</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E146" s="1">
         <v>145</v>
@@ -14905,16 +14902,16 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B147" s="1">
         <v>6</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E147" s="1">
         <v>146</v>
@@ -14946,16 +14943,16 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B148" s="1">
         <v>6</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E148" s="1">
         <v>147</v>
@@ -14987,16 +14984,16 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B149" s="1">
         <v>6</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E149" s="1">
         <v>148</v>
@@ -15028,16 +15025,16 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B150" s="1">
         <v>6</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E150" s="1">
         <v>149</v>
@@ -15069,16 +15066,16 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B151" s="1">
         <v>6</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E151" s="1">
         <v>150</v>
@@ -15110,16 +15107,16 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B152" s="1">
         <v>6</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E152" s="1">
         <v>151</v>
@@ -15151,16 +15148,16 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B153" s="1">
         <v>6</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E153" s="1">
         <v>152</v>
@@ -15192,16 +15189,16 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B154" s="1">
         <v>6</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E154" s="1">
         <v>153</v>
@@ -15233,16 +15230,16 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B155" s="1">
         <v>6</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E155" s="1">
         <v>154</v>
@@ -15274,16 +15271,16 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B156" s="1">
         <v>6</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E156" s="1">
         <v>155</v>
@@ -15315,16 +15312,16 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B157" s="1">
         <v>6</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E157" s="1">
         <v>156</v>
@@ -15356,16 +15353,16 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B158" s="1">
         <v>6</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E158" s="1">
         <v>157</v>
@@ -15397,16 +15394,16 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B159" s="1">
         <v>6</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E159" s="1">
         <v>158</v>
@@ -15438,16 +15435,16 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B160" s="1">
         <v>6</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E160" s="1">
         <v>159</v>
@@ -15479,16 +15476,16 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B161" s="1">
         <v>7</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E161" s="1">
         <v>160</v>
@@ -15520,16 +15517,16 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B162" s="1">
         <v>7</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E162" s="1">
         <v>161</v>
@@ -15561,16 +15558,16 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B163" s="1">
         <v>7</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E163" s="1">
         <v>162</v>
@@ -15602,16 +15599,16 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B164" s="1">
         <v>7</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E164" s="1">
         <v>163</v>
@@ -15643,16 +15640,16 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B165" s="1">
         <v>7</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E165" s="1">
         <v>164</v>
@@ -15684,16 +15681,16 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B166" s="1">
         <v>7</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E166" s="1">
         <v>165</v>
@@ -15725,16 +15722,16 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B167" s="1">
         <v>7</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E167" s="1">
         <v>166</v>
@@ -15766,16 +15763,16 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B168" s="1">
         <v>7</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E168" s="1">
         <v>167</v>
@@ -15807,16 +15804,16 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B169" s="1">
         <v>7</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E169" s="1">
         <v>168</v>
@@ -15848,16 +15845,16 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B170" s="1">
         <v>7</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E170" s="1">
         <v>169</v>
@@ -15889,16 +15886,16 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B171" s="1">
         <v>7</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E171" s="1">
         <v>170</v>
@@ -15930,16 +15927,16 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B172" s="1">
         <v>7</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E172" s="1">
         <v>171</v>
@@ -15971,16 +15968,16 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B173" s="1">
         <v>7</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E173" s="1">
         <v>172</v>
@@ -16012,16 +16009,16 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B174" s="1">
         <v>7</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E174" s="1">
         <v>173</v>
@@ -16053,16 +16050,16 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B175" s="1">
         <v>7</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E175" s="1">
         <v>174</v>
@@ -16094,16 +16091,16 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B176" s="1">
         <v>7</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E176" s="1">
         <v>175</v>
@@ -16135,16 +16132,16 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B177" s="1">
         <v>7</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E177" s="1">
         <v>176</v>
@@ -16176,16 +16173,16 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B178" s="1">
         <v>7</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E178" s="1">
         <v>177</v>
@@ -16217,16 +16214,16 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B179" s="1">
         <v>7</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E179" s="1">
         <v>178</v>
@@ -16258,16 +16255,16 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B180" s="1">
         <v>7</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E180" s="1">
         <v>179</v>
@@ -16299,16 +16296,16 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B181" s="1">
         <v>7</v>
       </c>
       <c r="C181" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="D181" s="1" t="s">
         <v>481</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>482</v>
       </c>
       <c r="E181" s="1">
         <v>180</v>
@@ -16340,16 +16337,16 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B182" s="1">
         <v>7</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E182" s="1">
         <v>181</v>
@@ -16381,16 +16378,16 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B183" s="1">
         <v>7</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E183" s="1">
         <v>182</v>
@@ -16422,16 +16419,16 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B184" s="1">
         <v>7</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E184" s="1">
         <v>183</v>
@@ -16463,16 +16460,16 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B185" s="1">
         <v>7</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E185" s="1">
         <v>184</v>
@@ -16504,16 +16501,16 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B186" s="1">
         <v>7</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E186" s="1">
         <v>185</v>
@@ -16545,16 +16542,16 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B187" s="1">
         <v>7</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E187" s="1">
         <v>186</v>
@@ -16586,16 +16583,16 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B188" s="1">
         <v>1</v>
       </c>
       <c r="C188" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>488</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>489</v>
       </c>
       <c r="E188" s="1">
         <v>187</v>
@@ -16627,16 +16624,16 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B189" s="1">
         <v>1</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E189" s="1">
         <v>188</v>
@@ -16668,16 +16665,16 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B190" s="1">
         <v>1</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E190" s="1">
         <v>189</v>
@@ -16709,16 +16706,16 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B191" s="1">
         <v>2</v>
       </c>
       <c r="C191" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="D191" s="1" t="s">
         <v>492</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>493</v>
       </c>
       <c r="E191" s="1">
         <v>190</v>
@@ -16750,16 +16747,16 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B192" s="1">
         <v>2</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E192" s="1">
         <v>191</v>
@@ -16791,16 +16788,16 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B193" s="1">
         <v>3</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E193" s="1">
         <v>192</v>
@@ -16832,16 +16829,16 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B194" s="1">
         <v>3</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E194" s="1">
         <v>193</v>
@@ -16873,16 +16870,16 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B195" s="1">
         <v>5</v>
       </c>
       <c r="C195" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="D195" s="1" t="s">
         <v>497</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>498</v>
       </c>
       <c r="E195" s="1">
         <v>194</v>
@@ -16914,16 +16911,16 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B196" s="1">
         <v>5</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E196" s="1">
         <v>195</v>
@@ -16955,16 +16952,16 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B197" s="1">
         <v>5</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E197" s="1">
         <v>196</v>
@@ -16996,16 +16993,16 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B198" s="1">
         <v>5</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E198" s="1">
         <v>197</v>
@@ -17037,16 +17034,16 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B199" s="1">
         <v>5</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E199" s="1">
         <v>198</v>
@@ -17078,16 +17075,16 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B200" s="1">
         <v>5</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E200" s="1">
         <v>199</v>
@@ -17119,16 +17116,16 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B201" s="1">
         <v>5</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E201" s="1">
         <v>200</v>
@@ -17160,16 +17157,16 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B202" s="1">
         <v>5</v>
       </c>
       <c r="C202" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="D202" s="1" t="s">
         <v>505</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>506</v>
       </c>
       <c r="E202" s="1">
         <v>201</v>
@@ -17201,16 +17198,16 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B203" s="1">
         <v>5</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E203" s="1">
         <v>202</v>
@@ -17242,16 +17239,16 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B204" s="1">
         <v>5</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E204" s="1">
         <v>203</v>
@@ -17283,16 +17280,16 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B205" s="1">
         <v>5</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E205" s="1">
         <v>204</v>
@@ -17324,16 +17321,16 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B206" s="1">
         <v>6</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E206" s="1">
         <v>205</v>
@@ -17365,16 +17362,16 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B207" s="1">
         <v>6</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E207" s="1">
         <v>206</v>
@@ -17406,16 +17403,16 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B208" s="1">
         <v>6</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E208" s="1">
         <v>207</v>
@@ -17447,16 +17444,16 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B209" s="1">
         <v>6</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E209" s="1">
         <v>208</v>
@@ -17488,16 +17485,16 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B210" s="1">
         <v>6</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E210" s="1">
         <v>209</v>
@@ -17529,16 +17526,16 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B211" s="1">
         <v>6</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E211" s="1">
         <v>210</v>
@@ -17570,16 +17567,16 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B212" s="1">
         <v>6</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E212" s="1">
         <v>211</v>
@@ -17611,16 +17608,16 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B213" s="1">
         <v>6</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E213" s="1">
         <v>212</v>
@@ -17652,16 +17649,16 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B214" s="1">
         <v>6</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E214" s="1">
         <v>213</v>
@@ -17693,16 +17690,16 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B215" s="1">
         <v>6</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E215" s="1">
         <v>214</v>
@@ -17734,16 +17731,16 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B216" s="1">
         <v>6</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E216" s="1">
         <v>215</v>
@@ -17775,16 +17772,16 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B217" s="1">
         <v>7</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E217" s="1">
         <v>216</v>
@@ -17816,16 +17813,16 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B218" s="1">
         <v>7</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E218" s="1">
         <v>217</v>
@@ -17857,16 +17854,16 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B219" s="1">
         <v>7</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E219" s="1">
         <v>218</v>
@@ -17898,16 +17895,16 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B220" s="1">
         <v>7</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E220" s="1">
         <v>219</v>
@@ -17939,16 +17936,16 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B221" s="1">
         <v>7</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E221" s="1">
         <v>220</v>
@@ -17980,16 +17977,16 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B222" s="1">
         <v>7</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E222" s="1">
         <v>221</v>
@@ -18021,16 +18018,16 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B223" s="1">
         <v>7</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E223" s="1">
         <v>222</v>
@@ -18062,16 +18059,16 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B224" s="1">
         <v>7</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E224" s="1">
         <v>223</v>
@@ -18103,16 +18100,16 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B225" s="1">
         <v>7</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E225" s="1">
         <v>224</v>
@@ -18144,16 +18141,16 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B226" s="1">
         <v>7</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E226" s="1">
         <v>225</v>
@@ -18185,16 +18182,16 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B227" s="1">
         <v>7</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E227" s="1">
         <v>226</v>
@@ -18226,16 +18223,16 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B228" s="1">
         <v>8</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E228" s="1">
         <v>227</v>
@@ -18267,16 +18264,16 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B229" s="1">
         <v>8</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E229" s="1">
         <v>228</v>
@@ -18308,16 +18305,16 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B230" s="1">
         <v>8</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E230" s="1">
         <v>229</v>
@@ -18349,16 +18346,16 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B231" s="1">
         <v>8</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E231" s="1">
         <v>230</v>
@@ -18390,16 +18387,16 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B232" s="1">
         <v>8</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E232" s="1">
         <v>231</v>
@@ -18431,16 +18428,16 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B233" s="1">
         <v>8</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E233" s="1">
         <v>232</v>
@@ -18472,16 +18469,16 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B234" s="1">
         <v>8</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E234" s="1">
         <v>233</v>
@@ -18513,16 +18510,16 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B235" s="1">
         <v>8</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E235" s="1">
         <v>234</v>
@@ -18554,16 +18551,16 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B236" s="1">
         <v>8</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E236" s="1">
         <v>235</v>
@@ -18595,16 +18592,16 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B237" s="1">
         <v>8</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E237" s="1">
         <v>236</v>
@@ -18636,16 +18633,16 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B238" s="1">
         <v>8</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E238" s="1">
         <v>237</v>
@@ -18677,16 +18674,16 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B239" s="1">
         <v>9</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E239" s="1">
         <v>238</v>
@@ -18718,16 +18715,16 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B240" s="1">
         <v>9</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E240" s="1">
         <v>239</v>
@@ -18759,16 +18756,16 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B241" s="1">
         <v>9</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E241" s="1">
         <v>240</v>
@@ -18800,16 +18797,16 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B242" s="1">
         <v>9</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E242" s="1">
         <v>241</v>
@@ -18841,16 +18838,16 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B243" s="1">
         <v>9</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E243" s="1">
         <v>242</v>
@@ -18882,16 +18879,16 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B244" s="1">
         <v>9</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E244" s="1">
         <v>243</v>
@@ -18923,16 +18920,16 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B245" s="1">
         <v>9</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E245" s="1">
         <v>244</v>
@@ -18964,16 +18961,16 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B246" s="1">
         <v>9</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E246" s="1">
         <v>245</v>
@@ -19005,16 +19002,16 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B247" s="1">
         <v>9</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E247" s="1">
         <v>246</v>
@@ -19046,16 +19043,16 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B248" s="1">
         <v>9</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E248" s="1">
         <v>247</v>
@@ -19087,16 +19084,16 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B249" s="1">
         <v>9</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E249" s="1">
         <v>248</v>
@@ -19128,16 +19125,16 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B250" s="1">
         <v>10</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E250" s="1">
         <v>249</v>
@@ -19169,16 +19166,16 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B251" s="1">
         <v>10</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E251" s="1">
         <v>250</v>
@@ -19210,16 +19207,16 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B252" s="1">
         <v>10</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E252" s="1">
         <v>251</v>
@@ -19251,16 +19248,16 @@
     </row>
     <row r="253">
       <c r="A253" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B253" s="1">
         <v>10</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E253" s="1">
         <v>252</v>
@@ -19292,16 +19289,16 @@
     </row>
     <row r="254">
       <c r="A254" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B254" s="1">
         <v>10</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E254" s="1">
         <v>253</v>
@@ -19333,16 +19330,16 @@
     </row>
     <row r="255">
       <c r="A255" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B255" s="1">
         <v>10</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E255" s="1">
         <v>254</v>
@@ -19374,16 +19371,16 @@
     </row>
     <row r="256">
       <c r="A256" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B256" s="1">
         <v>10</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E256" s="1">
         <v>255</v>
@@ -19415,16 +19412,16 @@
     </row>
     <row r="257">
       <c r="A257" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B257" s="1">
         <v>10</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E257" s="1">
         <v>256</v>
@@ -19456,16 +19453,16 @@
     </row>
     <row r="258">
       <c r="A258" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B258" s="1">
         <v>10</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E258" s="1">
         <v>257</v>
@@ -19497,16 +19494,16 @@
     </row>
     <row r="259">
       <c r="A259" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B259" s="1">
         <v>10</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E259" s="1">
         <v>258</v>
@@ -19538,16 +19535,16 @@
     </row>
     <row r="260">
       <c r="A260" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B260" s="1">
         <v>10</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E260" s="1">
         <v>259</v>
@@ -19579,16 +19576,16 @@
     </row>
     <row r="261">
       <c r="A261" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B261" s="1">
         <v>11</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E261" s="1">
         <v>260</v>
@@ -19620,16 +19617,16 @@
     </row>
     <row r="262">
       <c r="A262" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B262" s="1">
         <v>11</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E262" s="1">
         <v>261</v>
@@ -19661,16 +19658,16 @@
     </row>
     <row r="263">
       <c r="A263" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B263" s="1">
         <v>11</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E263" s="1">
         <v>262</v>
@@ -19702,16 +19699,16 @@
     </row>
     <row r="264">
       <c r="A264" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B264" s="1">
         <v>11</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E264" s="1">
         <v>263</v>
@@ -19743,16 +19740,16 @@
     </row>
     <row r="265">
       <c r="A265" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B265" s="1">
         <v>11</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E265" s="1">
         <v>264</v>
@@ -19784,16 +19781,16 @@
     </row>
     <row r="266">
       <c r="A266" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B266" s="1">
         <v>11</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E266" s="1">
         <v>265</v>
@@ -19825,16 +19822,16 @@
     </row>
     <row r="267">
       <c r="A267" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B267" s="1">
         <v>11</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E267" s="1">
         <v>266</v>
@@ -19866,16 +19863,16 @@
     </row>
     <row r="268">
       <c r="A268" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B268" s="1">
         <v>12</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E268" s="1">
         <v>267</v>
@@ -19907,16 +19904,16 @@
     </row>
     <row r="269">
       <c r="A269" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B269" s="1">
         <v>12</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E269" s="1">
         <v>268</v>
@@ -19948,16 +19945,16 @@
     </row>
     <row r="270">
       <c r="A270" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B270" s="1">
         <v>12</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E270" s="1">
         <v>269</v>
@@ -19989,16 +19986,16 @@
     </row>
     <row r="271">
       <c r="A271" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B271" s="1">
         <v>12</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E271" s="1">
         <v>270</v>
@@ -20030,16 +20027,16 @@
     </row>
     <row r="272">
       <c r="A272" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B272" s="1">
         <v>12</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E272" s="1">
         <v>271</v>
@@ -20071,16 +20068,16 @@
     </row>
     <row r="273">
       <c r="A273" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B273" s="1">
         <v>12</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E273" s="1">
         <v>272</v>
@@ -20112,16 +20109,16 @@
     </row>
     <row r="274">
       <c r="A274" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B274" s="1">
         <v>12</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E274" s="1">
         <v>273</v>
@@ -20153,16 +20150,16 @@
     </row>
     <row r="275">
       <c r="A275" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B275" s="1">
         <v>13</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E275" s="1">
         <v>274</v>
@@ -20194,16 +20191,16 @@
     </row>
     <row r="276">
       <c r="A276" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B276" s="1">
         <v>13</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E276" s="1">
         <v>275</v>
@@ -20235,16 +20232,16 @@
     </row>
     <row r="277">
       <c r="A277" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B277" s="1">
         <v>13</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E277" s="1">
         <v>276</v>
@@ -20276,16 +20273,16 @@
     </row>
     <row r="278">
       <c r="A278" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B278" s="1">
         <v>13</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E278" s="1">
         <v>277</v>
@@ -20317,16 +20314,16 @@
     </row>
     <row r="279">
       <c r="A279" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B279" s="1">
         <v>13</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E279" s="1">
         <v>278</v>
@@ -20358,16 +20355,16 @@
     </row>
     <row r="280">
       <c r="A280" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B280" s="1">
         <v>13</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E280" s="1">
         <v>279</v>
@@ -20399,16 +20396,16 @@
     </row>
     <row r="281">
       <c r="A281" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B281" s="1">
         <v>13</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E281" s="1">
         <v>280</v>
@@ -20440,16 +20437,16 @@
     </row>
     <row r="282">
       <c r="A282" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B282" s="1">
         <v>14</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E282" s="1">
         <v>281</v>
@@ -20481,16 +20478,16 @@
     </row>
     <row r="283">
       <c r="A283" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B283" s="1">
         <v>14</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E283" s="1">
         <v>282</v>
@@ -20522,16 +20519,16 @@
     </row>
     <row r="284">
       <c r="A284" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B284" s="1">
         <v>14</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E284" s="1">
         <v>283</v>
@@ -20563,16 +20560,16 @@
     </row>
     <row r="285">
       <c r="A285" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B285" s="1">
         <v>14</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E285" s="1">
         <v>284</v>
@@ -20604,16 +20601,16 @@
     </row>
     <row r="286">
       <c r="A286" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B286" s="1">
         <v>14</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E286" s="1">
         <v>285</v>
@@ -20645,16 +20642,16 @@
     </row>
     <row r="287">
       <c r="A287" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B287" s="1">
         <v>14</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E287" s="1">
         <v>286</v>
@@ -20686,16 +20683,16 @@
     </row>
     <row r="288">
       <c r="A288" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B288" s="1">
         <v>14</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E288" s="1">
         <v>287</v>
@@ -20727,16 +20724,16 @@
     </row>
     <row r="289">
       <c r="A289" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B289" s="1">
         <v>15</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E289" s="1">
         <v>288</v>
@@ -20768,16 +20765,16 @@
     </row>
     <row r="290">
       <c r="A290" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B290" s="1">
         <v>15</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E290" s="1">
         <v>289</v>
@@ -20809,16 +20806,16 @@
     </row>
     <row r="291">
       <c r="A291" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B291" s="1">
         <v>15</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E291" s="1">
         <v>290</v>
@@ -20850,16 +20847,16 @@
     </row>
     <row r="292">
       <c r="A292" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B292" s="1">
         <v>15</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E292" s="1">
         <v>291</v>
@@ -20891,16 +20888,16 @@
     </row>
     <row r="293">
       <c r="A293" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B293" s="1">
         <v>15</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E293" s="1">
         <v>292</v>
@@ -20932,16 +20929,16 @@
     </row>
     <row r="294">
       <c r="A294" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B294" s="1">
         <v>15</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E294" s="1">
         <v>293</v>
@@ -20973,16 +20970,16 @@
     </row>
     <row r="295">
       <c r="A295" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B295" s="1">
         <v>15</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E295" s="1">
         <v>294</v>
@@ -21014,16 +21011,16 @@
     </row>
     <row r="296">
       <c r="A296" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B296" s="1">
         <v>16</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E296" s="1">
         <v>295</v>
@@ -21055,16 +21052,16 @@
     </row>
     <row r="297">
       <c r="A297" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B297" s="1">
         <v>16</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E297" s="1">
         <v>296</v>
@@ -21096,16 +21093,16 @@
     </row>
     <row r="298">
       <c r="A298" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B298" s="1">
         <v>16</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E298" s="1">
         <v>297</v>
@@ -21137,16 +21134,16 @@
     </row>
     <row r="299">
       <c r="A299" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B299" s="1">
         <v>16</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E299" s="1">
         <v>298</v>
@@ -21178,16 +21175,16 @@
     </row>
     <row r="300">
       <c r="A300" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B300" s="1">
         <v>16</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E300" s="1">
         <v>299</v>
@@ -21219,16 +21216,16 @@
     </row>
     <row r="301">
       <c r="A301" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B301" s="1">
         <v>16</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E301" s="1">
         <v>300</v>
@@ -21260,16 +21257,16 @@
     </row>
     <row r="302">
       <c r="A302" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B302" s="1">
         <v>16</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E302" s="1">
         <v>301</v>
@@ -21301,16 +21298,16 @@
     </row>
     <row r="303">
       <c r="A303" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B303" s="1">
         <v>1</v>
       </c>
       <c r="C303" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D303" s="1" t="s">
         <v>527</v>
-      </c>
-      <c r="D303" s="1" t="s">
-        <v>528</v>
       </c>
       <c r="E303" s="1">
         <v>302</v>
@@ -21342,16 +21339,16 @@
     </row>
     <row r="304">
       <c r="A304" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B304" s="1">
         <v>1</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E304" s="1">
         <v>303</v>
@@ -21383,16 +21380,16 @@
     </row>
     <row r="305">
       <c r="A305" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B305" s="1">
         <v>1</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E305" s="1">
         <v>304</v>
@@ -21424,16 +21421,16 @@
     </row>
     <row r="306">
       <c r="A306" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B306" s="1">
         <v>1</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E306" s="1">
         <v>305</v>
@@ -21465,16 +21462,16 @@
     </row>
     <row r="307">
       <c r="A307" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B307" s="1">
         <v>1</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E307" s="1">
         <v>306</v>
@@ -21506,16 +21503,16 @@
     </row>
     <row r="308">
       <c r="A308" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B308" s="1">
         <v>1</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E308" s="1">
         <v>307</v>
@@ -21547,16 +21544,16 @@
     </row>
     <row r="309">
       <c r="A309" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B309" s="1">
         <v>1</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E309" s="1">
         <v>308</v>
@@ -21588,16 +21585,16 @@
     </row>
     <row r="310">
       <c r="A310" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B310" s="1">
         <v>1</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E310" s="1">
         <v>309</v>
@@ -21629,16 +21626,16 @@
     </row>
     <row r="311">
       <c r="A311" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B311" s="1">
         <v>1</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E311" s="1">
         <v>310</v>
@@ -21670,16 +21667,16 @@
     </row>
     <row r="312">
       <c r="A312" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B312" s="1">
         <v>1</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E312" s="1">
         <v>311</v>
@@ -21711,16 +21708,16 @@
     </row>
     <row r="313">
       <c r="A313" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B313" s="1">
         <v>1</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E313" s="1">
         <v>312</v>
@@ -21752,16 +21749,16 @@
     </row>
     <row r="314">
       <c r="A314" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B314" s="1">
         <v>1</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E314" s="1">
         <v>313</v>
@@ -21793,16 +21790,16 @@
     </row>
     <row r="315">
       <c r="A315" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B315" s="1">
         <v>1</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E315" s="1">
         <v>314</v>
@@ -21834,16 +21831,16 @@
     </row>
     <row r="316">
       <c r="A316" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B316" s="1">
         <v>1</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E316" s="1">
         <v>315</v>
@@ -21875,16 +21872,16 @@
     </row>
     <row r="317">
       <c r="A317" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B317" s="1">
         <v>1</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E317" s="1">
         <v>316</v>
@@ -21916,16 +21913,16 @@
     </row>
     <row r="318">
       <c r="A318" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B318" s="1">
         <v>1</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E318" s="1">
         <v>317</v>
@@ -21957,16 +21954,16 @@
     </row>
     <row r="319">
       <c r="A319" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B319" s="1">
         <v>1</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E319" s="1">
         <v>318</v>
@@ -21998,16 +21995,16 @@
     </row>
     <row r="320">
       <c r="A320" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B320" s="1">
         <v>1</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E320" s="1">
         <v>319</v>
@@ -22054,28 +22051,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>552</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>553</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>175</v>
@@ -22083,16 +22080,16 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>555</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>556</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -22106,16 +22103,16 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>558</v>
-      </c>
       <c r="C3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E3" s="1">
         <v>2</v>
@@ -22124,7 +22121,7 @@
         <v>15</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H3" s="1">
         <v>8</v>
@@ -22135,16 +22132,16 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>561</v>
-      </c>
       <c r="C4" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E4" s="1">
         <v>3</v>
@@ -22153,7 +22150,7 @@
         <v>15</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H4" s="1">
         <v>7</v>
@@ -22164,16 +22161,16 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>563</v>
-      </c>
       <c r="C5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E5" s="1">
         <v>4</v>
@@ -22182,7 +22179,7 @@
         <v>15</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H5" s="1">
         <v>11</v>
@@ -22193,16 +22190,16 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>565</v>
-      </c>
       <c r="C6" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E6" s="1">
         <v>5</v>
@@ -22216,16 +22213,16 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>567</v>
-      </c>
       <c r="C7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
@@ -22234,7 +22231,7 @@
         <v>15</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H7" s="1">
         <v>9</v>
@@ -22245,16 +22242,16 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>569</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>570</v>
       </c>
       <c r="E8" s="1">
         <v>7</v>
@@ -22268,16 +22265,16 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>572</v>
-      </c>
       <c r="C9" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E9" s="1">
         <v>8</v>
@@ -22286,7 +22283,7 @@
         <v>15</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H9" s="1">
         <v>17</v>
@@ -22297,16 +22294,16 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>574</v>
-      </c>
       <c r="C10" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E10" s="1">
         <v>9</v>
@@ -22315,7 +22312,7 @@
         <v>15</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H10" s="1">
         <v>16</v>
@@ -22326,16 +22323,16 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>576</v>
-      </c>
       <c r="C11" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E11" s="1">
         <v>10</v>
@@ -22344,7 +22341,7 @@
         <v>15</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>15</v>
@@ -22352,11 +22349,11 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>578</v>
-      </c>
       <c r="C12" s="1" t="s">
         <v>14</v>
       </c>
@@ -22364,7 +22361,7 @@
         <v>15</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H12" s="1">
         <v>1</v>
@@ -22372,11 +22369,11 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>580</v>
-      </c>
       <c r="C13" s="1" t="s">
         <v>14</v>
       </c>
@@ -22384,7 +22381,7 @@
         <v>15</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H13" s="1">
         <v>2</v>
@@ -22395,11 +22392,11 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>582</v>
-      </c>
       <c r="C14" s="1" t="s">
         <v>14</v>
       </c>
@@ -22407,7 +22404,7 @@
         <v>15</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H14" s="1">
         <v>3</v>
@@ -22418,11 +22415,11 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>584</v>
-      </c>
       <c r="C15" s="1" t="s">
         <v>14</v>
       </c>
@@ -22430,7 +22427,7 @@
         <v>15</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H15" s="1">
         <v>4</v>
@@ -22441,11 +22438,11 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>586</v>
-      </c>
       <c r="C16" s="1" t="s">
         <v>14</v>
       </c>
@@ -22453,7 +22450,7 @@
         <v>15</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H16" s="1">
         <v>5</v>
@@ -22464,11 +22461,11 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>588</v>
-      </c>
       <c r="C17" s="1" t="s">
         <v>14</v>
       </c>
@@ -22476,7 +22473,7 @@
         <v>15</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H17" s="1">
         <v>6</v>
@@ -22487,11 +22484,11 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>590</v>
-      </c>
       <c r="C18" s="1" t="s">
         <v>14</v>
       </c>
@@ -22499,7 +22496,7 @@
         <v>15</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H18" s="1">
         <v>10</v>
@@ -22510,11 +22507,11 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>592</v>
-      </c>
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -22522,7 +22519,7 @@
         <v>15</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H19" s="1">
         <v>12</v>
@@ -22533,11 +22530,11 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>594</v>
-      </c>
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -22545,7 +22542,7 @@
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H20" s="1">
         <v>13</v>
@@ -22556,11 +22553,11 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>596</v>
-      </c>
       <c r="C21" s="1" t="s">
         <v>14</v>
       </c>
@@ -22568,7 +22565,7 @@
         <v>15</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H21" s="1">
         <v>14</v>
@@ -22579,11 +22576,11 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>598</v>
-      </c>
       <c r="C22" s="1" t="s">
         <v>14</v>
       </c>
@@ -22591,7 +22588,7 @@
         <v>15</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H22" s="1">
         <v>15</v>
@@ -22602,11 +22599,11 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="C23" s="1" t="s">
         <v>14</v>
       </c>
@@ -22614,7 +22611,7 @@
         <v>15</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H23" s="1">
         <v>18</v>

--- a/Master Lists.xlsx
+++ b/Master Lists.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="7" activeTab="8"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="7" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Item Master" sheetId="1" r:id="rId1"/>
@@ -1018,13 +1018,13 @@
     <t>irshad89</t>
   </si>
   <si>
-    <t>Lim Choon Lian</t>
-  </si>
-  <si>
-    <t>Limcl</t>
-  </si>
-  <si>
-    <t>gosb3852</t>
+    <t>Captain Tomat</t>
+  </si>
+  <si>
+    <t>Tomatosup</t>
+  </si>
+  <si>
+    <t>campbell123</t>
   </si>
   <si>
     <t>Khin Kyaw Htwe</t>
@@ -20273,7 +20273,7 @@
         <v>273</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -20770,7 +20770,7 @@
     <col min="3" max="6" width="13.5" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.5">
+    <row r="1" ht="15">
       <c r="A1" s="8" t="s">
         <v>408</v>
       </c>
@@ -20790,7 +20790,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="2" ht="14.5">
+    <row r="2">
       <c r="A2" s="3" t="s">
         <v>410</v>
       </c>
@@ -20810,7 +20810,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" ht="14.5">
+    <row r="3">
       <c r="A3" s="3" t="s">
         <v>410</v>
       </c>
@@ -20830,7 +20830,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" ht="14.5">
+    <row r="4">
       <c r="A4" s="3" t="s">
         <v>414</v>
       </c>
@@ -20850,7 +20850,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" ht="14.5">
+    <row r="5">
       <c r="A5" s="3" t="s">
         <v>416</v>
       </c>
@@ -20870,7 +20870,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" ht="14.5">
+    <row r="6">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
@@ -20890,7 +20890,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" ht="14.5">
+    <row r="7">
       <c r="A7" s="3" t="s">
         <v>418</v>
       </c>
@@ -20910,7 +20910,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" ht="14.5">
+    <row r="8">
       <c r="A8" s="3" t="s">
         <v>420</v>
       </c>

--- a/Master Lists.xlsx
+++ b/Master Lists.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="7" activeTab="8"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="7"/>
   </bookViews>
   <sheets>
     <sheet name="Item Master" sheetId="1" r:id="rId1"/>
@@ -280,7 +280,7 @@
     <t>Disposable Gloves - L</t>
   </si>
   <si>
-    <t>Cable Tie 6"</t>
+    <t>Cable Tie 8"</t>
   </si>
   <si>
     <t>Magic Sponge</t>
@@ -21794,9 +21794,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
-        <v>83</v>
-      </c>
+      <c r="A5"/>
       <c r="B5" s="3" t="s">
         <v>185</v>
       </c>
@@ -22050,6 +22048,9 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="s">
+        <v>83</v>
+      </c>
       <c r="B37" s="3" t="s">
         <v>229</v>
       </c>
@@ -65393,7 +65394,6 @@
       <c r="JR118" s="1"/>
     </row>
     <row r="119">
-      <c r="HM119"/>
       <c r="HN119" s="1"/>
       <c r="HO119" s="1"/>
       <c r="HP119" s="1"/>
@@ -65453,7 +65453,6 @@
       <c r="JR119" s="1"/>
     </row>
     <row r="120">
-      <c r="HM120"/>
       <c r="HN120" s="1"/>
       <c r="HO120" s="1"/>
       <c r="HP120" s="1"/>
@@ -65513,7 +65512,6 @@
       <c r="JR120" s="1"/>
     </row>
     <row r="121">
-      <c r="HM121"/>
       <c r="HN121" s="1"/>
       <c r="HO121" s="1"/>
       <c r="HP121" s="1"/>
@@ -65573,7 +65571,6 @@
       <c r="JR121" s="1"/>
     </row>
     <row r="122">
-      <c r="HM122"/>
       <c r="HN122" s="1"/>
       <c r="HO122" s="1"/>
       <c r="HP122" s="1"/>
@@ -65633,7 +65630,6 @@
       <c r="JR122" s="1"/>
     </row>
     <row r="123">
-      <c r="HM123"/>
       <c r="HN123" s="1"/>
       <c r="HO123" s="1"/>
       <c r="HP123" s="1"/>
@@ -65693,7 +65689,6 @@
       <c r="JR123" s="1"/>
     </row>
     <row r="124">
-      <c r="HM124"/>
       <c r="HN124" s="1"/>
       <c r="HO124" s="1"/>
       <c r="HP124" s="1"/>
@@ -65753,7 +65748,6 @@
       <c r="JR124" s="1"/>
     </row>
     <row r="125">
-      <c r="HM125"/>
       <c r="HN125" s="1"/>
       <c r="HO125" s="1"/>
       <c r="HP125" s="1"/>
@@ -65813,7 +65807,6 @@
       <c r="JR125" s="1"/>
     </row>
     <row r="126">
-      <c r="HM126"/>
       <c r="HN126" s="1"/>
       <c r="HO126" s="1"/>
       <c r="HP126" s="1"/>
@@ -65873,7 +65866,6 @@
       <c r="JR126" s="1"/>
     </row>
     <row r="127">
-      <c r="HM127"/>
       <c r="HN127" s="1"/>
       <c r="HO127" s="1"/>
       <c r="HP127" s="1"/>
@@ -65933,7 +65925,6 @@
       <c r="JR127" s="1"/>
     </row>
     <row r="128">
-      <c r="HM128"/>
       <c r="HN128" s="1"/>
       <c r="HO128" s="1"/>
       <c r="HP128" s="1"/>
@@ -65993,7 +65984,6 @@
       <c r="JR128" s="1"/>
     </row>
     <row r="129">
-      <c r="HM129"/>
       <c r="HN129" s="1"/>
       <c r="HO129" s="1"/>
       <c r="HP129" s="1"/>
@@ -66053,7 +66043,6 @@
       <c r="JR129" s="1"/>
     </row>
     <row r="130">
-      <c r="HM130"/>
       <c r="HN130" s="1"/>
       <c r="HO130" s="1"/>
       <c r="HP130" s="1"/>
@@ -66113,7 +66102,6 @@
       <c r="JR130" s="1"/>
     </row>
     <row r="131">
-      <c r="HM131"/>
       <c r="HN131" s="1"/>
       <c r="HO131" s="1"/>
       <c r="HP131" s="1"/>
@@ -66173,7 +66161,6 @@
       <c r="JR131" s="1"/>
     </row>
     <row r="132">
-      <c r="HM132"/>
       <c r="HN132" s="1"/>
       <c r="HO132" s="1"/>
       <c r="HP132" s="1"/>
@@ -66233,7 +66220,6 @@
       <c r="JR132" s="1"/>
     </row>
     <row r="133">
-      <c r="HM133"/>
       <c r="HN133" s="1"/>
       <c r="HO133" s="1"/>
       <c r="HP133" s="1"/>
@@ -66293,7 +66279,6 @@
       <c r="JR133" s="1"/>
     </row>
     <row r="134">
-      <c r="HM134"/>
       <c r="HN134" s="1"/>
       <c r="HO134" s="1"/>
       <c r="HP134" s="1"/>
@@ -66353,7 +66338,6 @@
       <c r="JR134" s="1"/>
     </row>
     <row r="135">
-      <c r="HM135"/>
       <c r="HN135" s="1"/>
       <c r="HO135" s="1"/>
       <c r="HP135" s="1"/>
@@ -66413,7 +66397,6 @@
       <c r="JR135" s="1"/>
     </row>
     <row r="136">
-      <c r="HM136"/>
       <c r="HN136" s="1"/>
       <c r="HO136" s="1"/>
       <c r="HP136" s="1"/>
@@ -66473,7 +66456,6 @@
       <c r="JR136" s="1"/>
     </row>
     <row r="137">
-      <c r="HM137"/>
       <c r="HN137" s="1"/>
       <c r="HO137" s="1"/>
       <c r="HP137" s="1"/>
@@ -66533,7 +66515,6 @@
       <c r="JR137" s="1"/>
     </row>
     <row r="138">
-      <c r="HM138"/>
       <c r="HN138" s="1"/>
       <c r="HO138" s="1"/>
       <c r="HP138" s="1"/>
@@ -66593,7 +66574,6 @@
       <c r="JR138" s="1"/>
     </row>
     <row r="139">
-      <c r="HM139"/>
       <c r="HN139" s="1"/>
       <c r="HO139" s="1"/>
       <c r="HP139" s="1"/>
@@ -66653,7 +66633,6 @@
       <c r="JR139" s="1"/>
     </row>
     <row r="140">
-      <c r="HM140"/>
       <c r="HN140" s="1"/>
       <c r="HO140" s="1"/>
       <c r="HP140" s="1"/>

--- a/Master Lists.xlsx
+++ b/Master Lists.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="7" activeTab="10"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="7" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Item Master" sheetId="1" r:id="rId1"/>
@@ -38099,6 +38099,17 @@
       <c r="FG2" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ2" s="1"/>
+      <c r="GK2" s="1"/>
+      <c r="GL2" s="1"/>
+      <c r="GM2" s="1"/>
+      <c r="GN2" s="1"/>
+      <c r="GO2" s="1"/>
+      <c r="GP2" s="1"/>
+      <c r="GQ2" s="1"/>
+      <c r="GR2" s="1"/>
+      <c r="GS2" s="1"/>
+      <c r="GT2" s="1"/>
       <c r="GU2" s="1" t="s">
         <v>15</v>
       </c>
@@ -38196,6 +38207,17 @@
       <c r="FG3" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ3" s="1"/>
+      <c r="GK3" s="1"/>
+      <c r="GL3" s="1"/>
+      <c r="GM3" s="1"/>
+      <c r="GN3" s="1"/>
+      <c r="GO3" s="1"/>
+      <c r="GP3" s="1"/>
+      <c r="GQ3" s="1"/>
+      <c r="GR3" s="1"/>
+      <c r="GS3" s="1"/>
+      <c r="GT3" s="1"/>
       <c r="GU3" s="1" t="s">
         <v>15</v>
       </c>
@@ -38293,6 +38315,17 @@
       <c r="FG4" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ4" s="1"/>
+      <c r="GK4" s="1"/>
+      <c r="GL4" s="1"/>
+      <c r="GM4" s="1"/>
+      <c r="GN4" s="1"/>
+      <c r="GO4" s="1"/>
+      <c r="GP4" s="1"/>
+      <c r="GQ4" s="1"/>
+      <c r="GR4" s="1"/>
+      <c r="GS4" s="1"/>
+      <c r="GT4" s="1"/>
       <c r="GU4" s="1" t="s">
         <v>15</v>
       </c>
@@ -38390,6 +38423,17 @@
       <c r="FG5" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ5" s="1"/>
+      <c r="GK5" s="1"/>
+      <c r="GL5" s="1"/>
+      <c r="GM5" s="1"/>
+      <c r="GN5" s="1"/>
+      <c r="GO5" s="1"/>
+      <c r="GP5" s="1"/>
+      <c r="GQ5" s="1"/>
+      <c r="GR5" s="1"/>
+      <c r="GS5" s="1"/>
+      <c r="GT5" s="1"/>
       <c r="GU5" s="1" t="s">
         <v>15</v>
       </c>
@@ -38487,6 +38531,17 @@
       <c r="FG6" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ6" s="1"/>
+      <c r="GK6" s="1"/>
+      <c r="GL6" s="1"/>
+      <c r="GM6" s="1"/>
+      <c r="GN6" s="1"/>
+      <c r="GO6" s="1"/>
+      <c r="GP6" s="1"/>
+      <c r="GQ6" s="1"/>
+      <c r="GR6" s="1"/>
+      <c r="GS6" s="1"/>
+      <c r="GT6" s="1"/>
       <c r="GU6" s="1" t="s">
         <v>15</v>
       </c>
@@ -38584,6 +38639,17 @@
       <c r="FG7" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ7" s="1"/>
+      <c r="GK7" s="1"/>
+      <c r="GL7" s="1"/>
+      <c r="GM7" s="1"/>
+      <c r="GN7" s="1"/>
+      <c r="GO7" s="1"/>
+      <c r="GP7" s="1"/>
+      <c r="GQ7" s="1"/>
+      <c r="GR7" s="1"/>
+      <c r="GS7" s="1"/>
+      <c r="GT7" s="1"/>
       <c r="GU7" s="1" t="s">
         <v>15</v>
       </c>
@@ -38678,6 +38744,17 @@
       <c r="FG8" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ8" s="1"/>
+      <c r="GK8" s="1"/>
+      <c r="GL8" s="1"/>
+      <c r="GM8" s="1"/>
+      <c r="GN8" s="1"/>
+      <c r="GO8" s="1"/>
+      <c r="GP8" s="1"/>
+      <c r="GQ8" s="1"/>
+      <c r="GR8" s="1"/>
+      <c r="GS8" s="1"/>
+      <c r="GT8" s="1"/>
       <c r="GU8" s="1" t="s">
         <v>15</v>
       </c>
@@ -38772,6 +38849,17 @@
       <c r="FG9" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ9" s="1"/>
+      <c r="GK9" s="1"/>
+      <c r="GL9" s="1"/>
+      <c r="GM9" s="1"/>
+      <c r="GN9" s="1"/>
+      <c r="GO9" s="1"/>
+      <c r="GP9" s="1"/>
+      <c r="GQ9" s="1"/>
+      <c r="GR9" s="1"/>
+      <c r="GS9" s="1"/>
+      <c r="GT9" s="1"/>
       <c r="GU9" s="1" t="s">
         <v>15</v>
       </c>
@@ -38869,6 +38957,17 @@
       <c r="FG10" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ10" s="1"/>
+      <c r="GK10" s="1"/>
+      <c r="GL10" s="1"/>
+      <c r="GM10" s="1"/>
+      <c r="GN10" s="1"/>
+      <c r="GO10" s="1"/>
+      <c r="GP10" s="1"/>
+      <c r="GQ10" s="1"/>
+      <c r="GR10" s="1"/>
+      <c r="GS10" s="1"/>
+      <c r="GT10" s="1"/>
       <c r="GU10" s="1" t="s">
         <v>15</v>
       </c>
@@ -38966,6 +39065,17 @@
       <c r="FG11" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ11" s="1"/>
+      <c r="GK11" s="1"/>
+      <c r="GL11" s="1"/>
+      <c r="GM11" s="1"/>
+      <c r="GN11" s="1"/>
+      <c r="GO11" s="1"/>
+      <c r="GP11" s="1"/>
+      <c r="GQ11" s="1"/>
+      <c r="GR11" s="1"/>
+      <c r="GS11" s="1"/>
+      <c r="GT11" s="1"/>
       <c r="GU11" s="1" t="s">
         <v>15</v>
       </c>
@@ -39063,6 +39173,17 @@
       <c r="FG12" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ12" s="1"/>
+      <c r="GK12" s="1"/>
+      <c r="GL12" s="1"/>
+      <c r="GM12" s="1"/>
+      <c r="GN12" s="1"/>
+      <c r="GO12" s="1"/>
+      <c r="GP12" s="1"/>
+      <c r="GQ12" s="1"/>
+      <c r="GR12" s="1"/>
+      <c r="GS12" s="1"/>
+      <c r="GT12" s="1"/>
       <c r="GU12" s="1" t="s">
         <v>15</v>
       </c>
@@ -39157,6 +39278,17 @@
       <c r="FG13" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ13" s="1"/>
+      <c r="GK13" s="1"/>
+      <c r="GL13" s="1"/>
+      <c r="GM13" s="1"/>
+      <c r="GN13" s="1"/>
+      <c r="GO13" s="1"/>
+      <c r="GP13" s="1"/>
+      <c r="GQ13" s="1"/>
+      <c r="GR13" s="1"/>
+      <c r="GS13" s="1"/>
+      <c r="GT13" s="1"/>
       <c r="GU13" s="1" t="s">
         <v>15</v>
       </c>
@@ -39251,6 +39383,17 @@
       <c r="FG14" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ14" s="1"/>
+      <c r="GK14" s="1"/>
+      <c r="GL14" s="1"/>
+      <c r="GM14" s="1"/>
+      <c r="GN14" s="1"/>
+      <c r="GO14" s="1"/>
+      <c r="GP14" s="1"/>
+      <c r="GQ14" s="1"/>
+      <c r="GR14" s="1"/>
+      <c r="GS14" s="1"/>
+      <c r="GT14" s="1"/>
       <c r="GU14" s="1" t="s">
         <v>15</v>
       </c>
@@ -39351,6 +39494,17 @@
       <c r="FG15" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ15" s="1"/>
+      <c r="GK15" s="1"/>
+      <c r="GL15" s="1"/>
+      <c r="GM15" s="1"/>
+      <c r="GN15" s="1"/>
+      <c r="GO15" s="1"/>
+      <c r="GP15" s="1"/>
+      <c r="GQ15" s="1"/>
+      <c r="GR15" s="1"/>
+      <c r="GS15" s="1"/>
+      <c r="GT15" s="1"/>
       <c r="GU15" s="1" t="s">
         <v>15</v>
       </c>
@@ -39451,6 +39605,17 @@
       <c r="FG16" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ16" s="1"/>
+      <c r="GK16" s="1"/>
+      <c r="GL16" s="1"/>
+      <c r="GM16" s="1"/>
+      <c r="GN16" s="1"/>
+      <c r="GO16" s="1"/>
+      <c r="GP16" s="1"/>
+      <c r="GQ16" s="1"/>
+      <c r="GR16" s="1"/>
+      <c r="GS16" s="1"/>
+      <c r="GT16" s="1"/>
       <c r="GU16" s="1" t="s">
         <v>15</v>
       </c>
@@ -39551,6 +39716,17 @@
       <c r="FG17" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ17" s="1"/>
+      <c r="GK17" s="1"/>
+      <c r="GL17" s="1"/>
+      <c r="GM17" s="1"/>
+      <c r="GN17" s="1"/>
+      <c r="GO17" s="1"/>
+      <c r="GP17" s="1"/>
+      <c r="GQ17" s="1"/>
+      <c r="GR17" s="1"/>
+      <c r="GS17" s="1"/>
+      <c r="GT17" s="1"/>
       <c r="GU17" s="1" t="s">
         <v>15</v>
       </c>
@@ -39840,6 +40016,39 @@
       <c r="GI18" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="GK18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="GL18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="GM18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="GN18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="GO18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="GP18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="GQ18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="GR18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="GS18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="GT18" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="GU18" s="1" t="s">
         <v>15</v>
       </c>
@@ -39873,7 +40082,9 @@
         <v>15</v>
       </c>
       <c r="HO18" s="1"/>
-      <c r="HP18" s="1"/>
+      <c r="HP18" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="HQ18" s="1"/>
       <c r="HR18" s="1" t="s">
         <v>15</v>
@@ -39890,7 +40101,9 @@
         <v>15</v>
       </c>
       <c r="HX18" s="1"/>
-      <c r="HY18" s="1"/>
+      <c r="HY18" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="HZ18" s="1"/>
       <c r="IA18" s="1" t="s">
         <v>15</v>
@@ -39900,55 +40113,73 @@
         <v>15</v>
       </c>
       <c r="ID18" s="1"/>
-      <c r="IE18" s="1"/>
+      <c r="IE18" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="IF18" s="1"/>
       <c r="IG18" s="1" t="s">
         <v>15</v>
       </c>
       <c r="IH18" s="1"/>
-      <c r="II18" s="1"/>
+      <c r="II18" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="IJ18" s="1"/>
       <c r="IK18" s="1" t="s">
         <v>15</v>
       </c>
       <c r="IL18" s="1"/>
-      <c r="IM18" s="1"/>
+      <c r="IM18" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="IN18" s="1"/>
       <c r="IO18" s="1" t="s">
         <v>15</v>
       </c>
       <c r="IP18" s="1"/>
-      <c r="IQ18" s="1"/>
+      <c r="IQ18" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="IR18" s="1"/>
       <c r="IS18" s="1" t="s">
         <v>15</v>
       </c>
       <c r="IT18" s="1"/>
-      <c r="IU18" s="1"/>
+      <c r="IU18" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="IV18" s="1"/>
       <c r="IW18" s="1" t="s">
         <v>15</v>
       </c>
       <c r="IX18" s="1"/>
-      <c r="IY18" s="1"/>
+      <c r="IY18" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="IZ18" s="1"/>
       <c r="JA18" s="1" t="s">
         <v>15</v>
       </c>
       <c r="JB18" s="1"/>
-      <c r="JC18" s="1"/>
+      <c r="JC18" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="JD18" s="1"/>
       <c r="JE18" s="1" t="s">
         <v>15</v>
       </c>
       <c r="JF18" s="1"/>
-      <c r="JG18" s="1"/>
+      <c r="JG18" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="JH18" s="1"/>
       <c r="JI18" s="1" t="s">
         <v>15</v>
       </c>
       <c r="JJ18" s="1"/>
-      <c r="JK18" s="1"/>
+      <c r="JK18" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="JL18" s="1"/>
       <c r="JM18" s="1" t="s">
         <v>15</v>
@@ -40806,6 +41037,9 @@
       <c r="BZ21" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="CA21" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="CD21" s="1" t="s">
         <v>15</v>
       </c>
@@ -41947,39 +42181,17 @@
       <c r="GI23" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="GJ23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="GK23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="GL23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="GM23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="GN23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="GO23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="GP23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="GQ23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="GR23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="GS23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="GT23" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="GJ23" s="1"/>
+      <c r="GK23" s="1"/>
+      <c r="GL23" s="1"/>
+      <c r="GM23" s="1"/>
+      <c r="GN23" s="1"/>
+      <c r="GO23" s="1"/>
+      <c r="GP23" s="1"/>
+      <c r="GQ23" s="1"/>
+      <c r="GR23" s="1"/>
+      <c r="GS23" s="1"/>
+      <c r="GT23" s="1"/>
       <c r="GU23" s="1" t="s">
         <v>15</v>
       </c>
@@ -42030,9 +42242,7 @@
         <v>15</v>
       </c>
       <c r="HO23" s="1"/>
-      <c r="HP23" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="HP23" s="1"/>
       <c r="HQ23" s="1"/>
       <c r="HR23" s="1" t="s">
         <v>15</v>
@@ -42049,9 +42259,7 @@
         <v>15</v>
       </c>
       <c r="HX23" s="1"/>
-      <c r="HY23" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="HY23" s="1"/>
       <c r="HZ23" s="1"/>
       <c r="IA23" s="1" t="s">
         <v>15</v>
@@ -42061,73 +42269,55 @@
         <v>15</v>
       </c>
       <c r="ID23" s="1"/>
-      <c r="IE23" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="IE23" s="1"/>
       <c r="IF23" s="1"/>
       <c r="IG23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="IH23" s="1"/>
-      <c r="II23" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="II23" s="1"/>
       <c r="IJ23" s="1"/>
       <c r="IK23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="IL23" s="1"/>
-      <c r="IM23" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="IM23" s="1"/>
       <c r="IN23" s="1"/>
       <c r="IO23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="IP23" s="1"/>
-      <c r="IQ23" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="IQ23" s="1"/>
       <c r="IR23" s="1"/>
       <c r="IS23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="IT23" s="1"/>
-      <c r="IU23" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="IU23" s="1"/>
       <c r="IV23" s="1"/>
       <c r="IW23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="IX23" s="1"/>
-      <c r="IY23" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="IY23" s="1"/>
       <c r="IZ23" s="1"/>
       <c r="JA23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="JB23" s="1"/>
-      <c r="JC23" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="JC23" s="1"/>
       <c r="JD23" s="1"/>
       <c r="JE23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="JF23" s="1"/>
-      <c r="JG23" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="JG23" s="1"/>
       <c r="JH23" s="1"/>
       <c r="JI23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="JJ23" s="1"/>
-      <c r="JK23" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="JK23" s="1"/>
       <c r="JL23" s="1"/>
       <c r="JM23" s="1" t="s">
         <v>15</v>
@@ -42235,6 +42425,17 @@
       <c r="FN24" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ24" s="1"/>
+      <c r="GK24" s="1"/>
+      <c r="GL24" s="1"/>
+      <c r="GM24" s="1"/>
+      <c r="GN24" s="1"/>
+      <c r="GO24" s="1"/>
+      <c r="GP24" s="1"/>
+      <c r="GQ24" s="1"/>
+      <c r="GR24" s="1"/>
+      <c r="GS24" s="1"/>
+      <c r="GT24" s="1"/>
       <c r="GU24" s="1" t="s">
         <v>15</v>
       </c>
@@ -42341,6 +42542,17 @@
       <c r="FM25" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ25" s="1"/>
+      <c r="GK25" s="1"/>
+      <c r="GL25" s="1"/>
+      <c r="GM25" s="1"/>
+      <c r="GN25" s="1"/>
+      <c r="GO25" s="1"/>
+      <c r="GP25" s="1"/>
+      <c r="GQ25" s="1"/>
+      <c r="GR25" s="1"/>
+      <c r="GS25" s="1"/>
+      <c r="GT25" s="1"/>
       <c r="GU25" s="1" t="s">
         <v>15</v>
       </c>
@@ -42438,6 +42650,17 @@
       <c r="FG26" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ26" s="1"/>
+      <c r="GK26" s="1"/>
+      <c r="GL26" s="1"/>
+      <c r="GM26" s="1"/>
+      <c r="GN26" s="1"/>
+      <c r="GO26" s="1"/>
+      <c r="GP26" s="1"/>
+      <c r="GQ26" s="1"/>
+      <c r="GR26" s="1"/>
+      <c r="GS26" s="1"/>
+      <c r="GT26" s="1"/>
       <c r="GU26" s="1" t="s">
         <v>15</v>
       </c>
@@ -42535,6 +42758,17 @@
       <c r="FG27" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ27" s="1"/>
+      <c r="GK27" s="1"/>
+      <c r="GL27" s="1"/>
+      <c r="GM27" s="1"/>
+      <c r="GN27" s="1"/>
+      <c r="GO27" s="1"/>
+      <c r="GP27" s="1"/>
+      <c r="GQ27" s="1"/>
+      <c r="GR27" s="1"/>
+      <c r="GS27" s="1"/>
+      <c r="GT27" s="1"/>
       <c r="GU27" s="1" t="s">
         <v>15</v>
       </c>
@@ -42632,6 +42866,17 @@
       <c r="FG28" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ28" s="1"/>
+      <c r="GK28" s="1"/>
+      <c r="GL28" s="1"/>
+      <c r="GM28" s="1"/>
+      <c r="GN28" s="1"/>
+      <c r="GO28" s="1"/>
+      <c r="GP28" s="1"/>
+      <c r="GQ28" s="1"/>
+      <c r="GR28" s="1"/>
+      <c r="GS28" s="1"/>
+      <c r="GT28" s="1"/>
       <c r="GU28" s="1" t="s">
         <v>15</v>
       </c>
@@ -42741,6 +42986,17 @@
       <c r="FN29" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ29" s="1"/>
+      <c r="GK29" s="1"/>
+      <c r="GL29" s="1"/>
+      <c r="GM29" s="1"/>
+      <c r="GN29" s="1"/>
+      <c r="GO29" s="1"/>
+      <c r="GP29" s="1"/>
+      <c r="GQ29" s="1"/>
+      <c r="GR29" s="1"/>
+      <c r="GS29" s="1"/>
+      <c r="GT29" s="1"/>
       <c r="GU29" s="1" t="s">
         <v>15</v>
       </c>
@@ -42838,6 +43094,17 @@
       <c r="FG30" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ30" s="1"/>
+      <c r="GK30" s="1"/>
+      <c r="GL30" s="1"/>
+      <c r="GM30" s="1"/>
+      <c r="GN30" s="1"/>
+      <c r="GO30" s="1"/>
+      <c r="GP30" s="1"/>
+      <c r="GQ30" s="1"/>
+      <c r="GR30" s="1"/>
+      <c r="GS30" s="1"/>
+      <c r="GT30" s="1"/>
       <c r="GU30" s="1" t="s">
         <v>15</v>
       </c>
@@ -42932,6 +43199,17 @@
       <c r="FG31" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ31" s="1"/>
+      <c r="GK31" s="1"/>
+      <c r="GL31" s="1"/>
+      <c r="GM31" s="1"/>
+      <c r="GN31" s="1"/>
+      <c r="GO31" s="1"/>
+      <c r="GP31" s="1"/>
+      <c r="GQ31" s="1"/>
+      <c r="GR31" s="1"/>
+      <c r="GS31" s="1"/>
+      <c r="GT31" s="1"/>
       <c r="GU31" s="1" t="s">
         <v>15</v>
       </c>
@@ -43029,6 +43307,17 @@
       <c r="FG32" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ32" s="1"/>
+      <c r="GK32" s="1"/>
+      <c r="GL32" s="1"/>
+      <c r="GM32" s="1"/>
+      <c r="GN32" s="1"/>
+      <c r="GO32" s="1"/>
+      <c r="GP32" s="1"/>
+      <c r="GQ32" s="1"/>
+      <c r="GR32" s="1"/>
+      <c r="GS32" s="1"/>
+      <c r="GT32" s="1"/>
       <c r="GU32" s="1" t="s">
         <v>15</v>
       </c>
@@ -43123,6 +43412,17 @@
       <c r="FG33" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ33" s="1"/>
+      <c r="GK33" s="1"/>
+      <c r="GL33" s="1"/>
+      <c r="GM33" s="1"/>
+      <c r="GN33" s="1"/>
+      <c r="GO33" s="1"/>
+      <c r="GP33" s="1"/>
+      <c r="GQ33" s="1"/>
+      <c r="GR33" s="1"/>
+      <c r="GS33" s="1"/>
+      <c r="GT33" s="1"/>
       <c r="GU33" s="1" t="s">
         <v>15</v>
       </c>
@@ -43220,6 +43520,17 @@
       <c r="FG34" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ34" s="1"/>
+      <c r="GK34" s="1"/>
+      <c r="GL34" s="1"/>
+      <c r="GM34" s="1"/>
+      <c r="GN34" s="1"/>
+      <c r="GO34" s="1"/>
+      <c r="GP34" s="1"/>
+      <c r="GQ34" s="1"/>
+      <c r="GR34" s="1"/>
+      <c r="GS34" s="1"/>
+      <c r="GT34" s="1"/>
       <c r="GU34" s="1" t="s">
         <v>15</v>
       </c>
@@ -43317,6 +43628,17 @@
       <c r="FG35" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ35" s="1"/>
+      <c r="GK35" s="1"/>
+      <c r="GL35" s="1"/>
+      <c r="GM35" s="1"/>
+      <c r="GN35" s="1"/>
+      <c r="GO35" s="1"/>
+      <c r="GP35" s="1"/>
+      <c r="GQ35" s="1"/>
+      <c r="GR35" s="1"/>
+      <c r="GS35" s="1"/>
+      <c r="GT35" s="1"/>
       <c r="GU35" s="1" t="s">
         <v>15</v>
       </c>
@@ -43414,6 +43736,17 @@
       <c r="FG36" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ36" s="1"/>
+      <c r="GK36" s="1"/>
+      <c r="GL36" s="1"/>
+      <c r="GM36" s="1"/>
+      <c r="GN36" s="1"/>
+      <c r="GO36" s="1"/>
+      <c r="GP36" s="1"/>
+      <c r="GQ36" s="1"/>
+      <c r="GR36" s="1"/>
+      <c r="GS36" s="1"/>
+      <c r="GT36" s="1"/>
       <c r="GU36" s="1" t="s">
         <v>15</v>
       </c>
@@ -43508,6 +43841,17 @@
       <c r="FG37" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ37" s="1"/>
+      <c r="GK37" s="1"/>
+      <c r="GL37" s="1"/>
+      <c r="GM37" s="1"/>
+      <c r="GN37" s="1"/>
+      <c r="GO37" s="1"/>
+      <c r="GP37" s="1"/>
+      <c r="GQ37" s="1"/>
+      <c r="GR37" s="1"/>
+      <c r="GS37" s="1"/>
+      <c r="GT37" s="1"/>
       <c r="GU37" s="1" t="s">
         <v>15</v>
       </c>
@@ -43602,6 +43946,17 @@
       <c r="FG38" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ38" s="1"/>
+      <c r="GK38" s="1"/>
+      <c r="GL38" s="1"/>
+      <c r="GM38" s="1"/>
+      <c r="GN38" s="1"/>
+      <c r="GO38" s="1"/>
+      <c r="GP38" s="1"/>
+      <c r="GQ38" s="1"/>
+      <c r="GR38" s="1"/>
+      <c r="GS38" s="1"/>
+      <c r="GT38" s="1"/>
       <c r="GU38" s="1" t="s">
         <v>15</v>
       </c>
@@ -43696,6 +44051,17 @@
       <c r="FG39" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ39" s="1"/>
+      <c r="GK39" s="1"/>
+      <c r="GL39" s="1"/>
+      <c r="GM39" s="1"/>
+      <c r="GN39" s="1"/>
+      <c r="GO39" s="1"/>
+      <c r="GP39" s="1"/>
+      <c r="GQ39" s="1"/>
+      <c r="GR39" s="1"/>
+      <c r="GS39" s="1"/>
+      <c r="GT39" s="1"/>
       <c r="GU39" s="1" t="s">
         <v>15</v>
       </c>
@@ -43790,6 +44156,17 @@
       <c r="FG40" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ40" s="1"/>
+      <c r="GK40" s="1"/>
+      <c r="GL40" s="1"/>
+      <c r="GM40" s="1"/>
+      <c r="GN40" s="1"/>
+      <c r="GO40" s="1"/>
+      <c r="GP40" s="1"/>
+      <c r="GQ40" s="1"/>
+      <c r="GR40" s="1"/>
+      <c r="GS40" s="1"/>
+      <c r="GT40" s="1"/>
       <c r="GU40" s="1" t="s">
         <v>15</v>
       </c>
@@ -43884,6 +44261,17 @@
       <c r="FG41" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ41" s="1"/>
+      <c r="GK41" s="1"/>
+      <c r="GL41" s="1"/>
+      <c r="GM41" s="1"/>
+      <c r="GN41" s="1"/>
+      <c r="GO41" s="1"/>
+      <c r="GP41" s="1"/>
+      <c r="GQ41" s="1"/>
+      <c r="GR41" s="1"/>
+      <c r="GS41" s="1"/>
+      <c r="GT41" s="1"/>
       <c r="GU41" s="1" t="s">
         <v>15</v>
       </c>
@@ -44257,6 +44645,17 @@
       <c r="FQ42" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ42" s="1"/>
+      <c r="GK42" s="1"/>
+      <c r="GL42" s="1"/>
+      <c r="GM42" s="1"/>
+      <c r="GN42" s="1"/>
+      <c r="GO42" s="1"/>
+      <c r="GP42" s="1"/>
+      <c r="GQ42" s="1"/>
+      <c r="GR42" s="1"/>
+      <c r="GS42" s="1"/>
+      <c r="GT42" s="1"/>
       <c r="GU42" s="1" t="s">
         <v>15</v>
       </c>
@@ -44742,6 +45141,17 @@
       <c r="FQ43" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ43" s="1"/>
+      <c r="GK43" s="1"/>
+      <c r="GL43" s="1"/>
+      <c r="GM43" s="1"/>
+      <c r="GN43" s="1"/>
+      <c r="GO43" s="1"/>
+      <c r="GP43" s="1"/>
+      <c r="GQ43" s="1"/>
+      <c r="GR43" s="1"/>
+      <c r="GS43" s="1"/>
+      <c r="GT43" s="1"/>
       <c r="GU43" s="1" t="s">
         <v>15</v>
       </c>
@@ -45236,6 +45646,17 @@
       <c r="FQ44" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ44" s="1"/>
+      <c r="GK44" s="1"/>
+      <c r="GL44" s="1"/>
+      <c r="GM44" s="1"/>
+      <c r="GN44" s="1"/>
+      <c r="GO44" s="1"/>
+      <c r="GP44" s="1"/>
+      <c r="GQ44" s="1"/>
+      <c r="GR44" s="1"/>
+      <c r="GS44" s="1"/>
+      <c r="GT44" s="1"/>
       <c r="GU44" s="1" t="s">
         <v>15</v>
       </c>
@@ -45673,6 +46094,17 @@
       <c r="FQ45" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ45" s="1"/>
+      <c r="GK45" s="1"/>
+      <c r="GL45" s="1"/>
+      <c r="GM45" s="1"/>
+      <c r="GN45" s="1"/>
+      <c r="GO45" s="1"/>
+      <c r="GP45" s="1"/>
+      <c r="GQ45" s="1"/>
+      <c r="GR45" s="1"/>
+      <c r="GS45" s="1"/>
+      <c r="GT45" s="1"/>
       <c r="GU45" s="1" t="s">
         <v>15</v>
       </c>
@@ -46672,6 +47104,17 @@
       <c r="FG47" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ47" s="1"/>
+      <c r="GK47" s="1"/>
+      <c r="GL47" s="1"/>
+      <c r="GM47" s="1"/>
+      <c r="GN47" s="1"/>
+      <c r="GO47" s="1"/>
+      <c r="GP47" s="1"/>
+      <c r="GQ47" s="1"/>
+      <c r="GR47" s="1"/>
+      <c r="GS47" s="1"/>
+      <c r="GT47" s="1"/>
       <c r="GU47" s="1" t="s">
         <v>15</v>
       </c>
@@ -47127,6 +47570,17 @@
       <c r="FQ48" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ48" s="1"/>
+      <c r="GK48" s="1"/>
+      <c r="GL48" s="1"/>
+      <c r="GM48" s="1"/>
+      <c r="GN48" s="1"/>
+      <c r="GO48" s="1"/>
+      <c r="GP48" s="1"/>
+      <c r="GQ48" s="1"/>
+      <c r="GR48" s="1"/>
+      <c r="GS48" s="1"/>
+      <c r="GT48" s="1"/>
       <c r="GU48" s="1" t="s">
         <v>15</v>
       </c>
@@ -47612,6 +48066,17 @@
       <c r="FQ49" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ49" s="1"/>
+      <c r="GK49" s="1"/>
+      <c r="GL49" s="1"/>
+      <c r="GM49" s="1"/>
+      <c r="GN49" s="1"/>
+      <c r="GO49" s="1"/>
+      <c r="GP49" s="1"/>
+      <c r="GQ49" s="1"/>
+      <c r="GR49" s="1"/>
+      <c r="GS49" s="1"/>
+      <c r="GT49" s="1"/>
       <c r="GU49" s="1" t="s">
         <v>15</v>
       </c>
@@ -48106,6 +48571,17 @@
       <c r="FQ50" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ50" s="1"/>
+      <c r="GK50" s="1"/>
+      <c r="GL50" s="1"/>
+      <c r="GM50" s="1"/>
+      <c r="GN50" s="1"/>
+      <c r="GO50" s="1"/>
+      <c r="GP50" s="1"/>
+      <c r="GQ50" s="1"/>
+      <c r="GR50" s="1"/>
+      <c r="GS50" s="1"/>
+      <c r="GT50" s="1"/>
       <c r="GU50" s="1" t="s">
         <v>15</v>
       </c>
@@ -48543,6 +49019,17 @@
       <c r="FQ51" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ51" s="1"/>
+      <c r="GK51" s="1"/>
+      <c r="GL51" s="1"/>
+      <c r="GM51" s="1"/>
+      <c r="GN51" s="1"/>
+      <c r="GO51" s="1"/>
+      <c r="GP51" s="1"/>
+      <c r="GQ51" s="1"/>
+      <c r="GR51" s="1"/>
+      <c r="GS51" s="1"/>
+      <c r="GT51" s="1"/>
       <c r="GU51" s="1" t="s">
         <v>15</v>
       </c>
@@ -49542,6 +50029,17 @@
       <c r="FG53" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ53" s="1"/>
+      <c r="GK53" s="1"/>
+      <c r="GL53" s="1"/>
+      <c r="GM53" s="1"/>
+      <c r="GN53" s="1"/>
+      <c r="GO53" s="1"/>
+      <c r="GP53" s="1"/>
+      <c r="GQ53" s="1"/>
+      <c r="GR53" s="1"/>
+      <c r="GS53" s="1"/>
+      <c r="GT53" s="1"/>
       <c r="GU53" s="1" t="s">
         <v>15</v>
       </c>
@@ -50003,6 +50501,17 @@
       <c r="FQ54" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ54" s="1"/>
+      <c r="GK54" s="1"/>
+      <c r="GL54" s="1"/>
+      <c r="GM54" s="1"/>
+      <c r="GN54" s="1"/>
+      <c r="GO54" s="1"/>
+      <c r="GP54" s="1"/>
+      <c r="GQ54" s="1"/>
+      <c r="GR54" s="1"/>
+      <c r="GS54" s="1"/>
+      <c r="GT54" s="1"/>
       <c r="GU54" s="1" t="s">
         <v>15</v>
       </c>
@@ -50488,6 +50997,17 @@
       <c r="FQ55" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ55" s="1"/>
+      <c r="GK55" s="1"/>
+      <c r="GL55" s="1"/>
+      <c r="GM55" s="1"/>
+      <c r="GN55" s="1"/>
+      <c r="GO55" s="1"/>
+      <c r="GP55" s="1"/>
+      <c r="GQ55" s="1"/>
+      <c r="GR55" s="1"/>
+      <c r="GS55" s="1"/>
+      <c r="GT55" s="1"/>
       <c r="GU55" s="1" t="s">
         <v>15</v>
       </c>
@@ -50988,6 +51508,17 @@
       <c r="FQ56" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ56" s="1"/>
+      <c r="GK56" s="1"/>
+      <c r="GL56" s="1"/>
+      <c r="GM56" s="1"/>
+      <c r="GN56" s="1"/>
+      <c r="GO56" s="1"/>
+      <c r="GP56" s="1"/>
+      <c r="GQ56" s="1"/>
+      <c r="GR56" s="1"/>
+      <c r="GS56" s="1"/>
+      <c r="GT56" s="1"/>
       <c r="GU56" s="1" t="s">
         <v>15</v>
       </c>
@@ -51431,6 +51962,17 @@
       <c r="FQ57" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ57" s="1"/>
+      <c r="GK57" s="1"/>
+      <c r="GL57" s="1"/>
+      <c r="GM57" s="1"/>
+      <c r="GN57" s="1"/>
+      <c r="GO57" s="1"/>
+      <c r="GP57" s="1"/>
+      <c r="GQ57" s="1"/>
+      <c r="GR57" s="1"/>
+      <c r="GS57" s="1"/>
+      <c r="GT57" s="1"/>
       <c r="GU57" s="1" t="s">
         <v>15</v>
       </c>
@@ -52436,6 +52978,17 @@
       <c r="FG59" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ59" s="1"/>
+      <c r="GK59" s="1"/>
+      <c r="GL59" s="1"/>
+      <c r="GM59" s="1"/>
+      <c r="GN59" s="1"/>
+      <c r="GO59" s="1"/>
+      <c r="GP59" s="1"/>
+      <c r="GQ59" s="1"/>
+      <c r="GR59" s="1"/>
+      <c r="GS59" s="1"/>
+      <c r="GT59" s="1"/>
       <c r="GU59" s="1" t="s">
         <v>15</v>
       </c>
@@ -52897,6 +53450,17 @@
       <c r="FQ60" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ60" s="1"/>
+      <c r="GK60" s="1"/>
+      <c r="GL60" s="1"/>
+      <c r="GM60" s="1"/>
+      <c r="GN60" s="1"/>
+      <c r="GO60" s="1"/>
+      <c r="GP60" s="1"/>
+      <c r="GQ60" s="1"/>
+      <c r="GR60" s="1"/>
+      <c r="GS60" s="1"/>
+      <c r="GT60" s="1"/>
       <c r="GU60" s="1" t="s">
         <v>15</v>
       </c>
@@ -53382,6 +53946,17 @@
       <c r="FQ61" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ61" s="1"/>
+      <c r="GK61" s="1"/>
+      <c r="GL61" s="1"/>
+      <c r="GM61" s="1"/>
+      <c r="GN61" s="1"/>
+      <c r="GO61" s="1"/>
+      <c r="GP61" s="1"/>
+      <c r="GQ61" s="1"/>
+      <c r="GR61" s="1"/>
+      <c r="GS61" s="1"/>
+      <c r="GT61" s="1"/>
       <c r="GU61" s="1" t="s">
         <v>15</v>
       </c>
@@ -53882,6 +54457,17 @@
       <c r="FQ62" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ62" s="1"/>
+      <c r="GK62" s="1"/>
+      <c r="GL62" s="1"/>
+      <c r="GM62" s="1"/>
+      <c r="GN62" s="1"/>
+      <c r="GO62" s="1"/>
+      <c r="GP62" s="1"/>
+      <c r="GQ62" s="1"/>
+      <c r="GR62" s="1"/>
+      <c r="GS62" s="1"/>
+      <c r="GT62" s="1"/>
       <c r="GU62" s="1" t="s">
         <v>15</v>
       </c>
@@ -54325,6 +54911,17 @@
       <c r="FQ63" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ63" s="1"/>
+      <c r="GK63" s="1"/>
+      <c r="GL63" s="1"/>
+      <c r="GM63" s="1"/>
+      <c r="GN63" s="1"/>
+      <c r="GO63" s="1"/>
+      <c r="GP63" s="1"/>
+      <c r="GQ63" s="1"/>
+      <c r="GR63" s="1"/>
+      <c r="GS63" s="1"/>
+      <c r="GT63" s="1"/>
       <c r="GU63" s="1" t="s">
         <v>15</v>
       </c>
@@ -55330,6 +55927,17 @@
       <c r="FG65" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ65" s="1"/>
+      <c r="GK65" s="1"/>
+      <c r="GL65" s="1"/>
+      <c r="GM65" s="1"/>
+      <c r="GN65" s="1"/>
+      <c r="GO65" s="1"/>
+      <c r="GP65" s="1"/>
+      <c r="GQ65" s="1"/>
+      <c r="GR65" s="1"/>
+      <c r="GS65" s="1"/>
+      <c r="GT65" s="1"/>
       <c r="GU65" s="1" t="s">
         <v>15</v>
       </c>
@@ -55722,6 +56330,17 @@
       <c r="FQ66" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ66" s="1"/>
+      <c r="GK66" s="1"/>
+      <c r="GL66" s="1"/>
+      <c r="GM66" s="1"/>
+      <c r="GN66" s="1"/>
+      <c r="GO66" s="1"/>
+      <c r="GP66" s="1"/>
+      <c r="GQ66" s="1"/>
+      <c r="GR66" s="1"/>
+      <c r="GS66" s="1"/>
+      <c r="GT66" s="1"/>
       <c r="GU66" s="1" t="s">
         <v>15</v>
       </c>
@@ -56670,6 +57289,17 @@
       <c r="FQ68" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ68" s="1"/>
+      <c r="GK68" s="1"/>
+      <c r="GL68" s="1"/>
+      <c r="GM68" s="1"/>
+      <c r="GN68" s="1"/>
+      <c r="GO68" s="1"/>
+      <c r="GP68" s="1"/>
+      <c r="GQ68" s="1"/>
+      <c r="GR68" s="1"/>
+      <c r="GS68" s="1"/>
+      <c r="GT68" s="1"/>
       <c r="GU68" s="1" t="s">
         <v>15</v>
       </c>
@@ -57134,6 +57764,17 @@
       <c r="FQ69" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ69" s="1"/>
+      <c r="GK69" s="1"/>
+      <c r="GL69" s="1"/>
+      <c r="GM69" s="1"/>
+      <c r="GN69" s="1"/>
+      <c r="GO69" s="1"/>
+      <c r="GP69" s="1"/>
+      <c r="GQ69" s="1"/>
+      <c r="GR69" s="1"/>
+      <c r="GS69" s="1"/>
+      <c r="GT69" s="1"/>
       <c r="GU69" s="1" t="s">
         <v>15</v>
       </c>
@@ -57590,6 +58231,17 @@
       <c r="FQ70" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ70" s="1"/>
+      <c r="GK70" s="1"/>
+      <c r="GL70" s="1"/>
+      <c r="GM70" s="1"/>
+      <c r="GN70" s="1"/>
+      <c r="GO70" s="1"/>
+      <c r="GP70" s="1"/>
+      <c r="GQ70" s="1"/>
+      <c r="GR70" s="1"/>
+      <c r="GS70" s="1"/>
+      <c r="GT70" s="1"/>
       <c r="GU70" s="1" t="s">
         <v>15</v>
       </c>
@@ -58049,6 +58701,17 @@
       <c r="FQ71" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ71" s="1"/>
+      <c r="GK71" s="1"/>
+      <c r="GL71" s="1"/>
+      <c r="GM71" s="1"/>
+      <c r="GN71" s="1"/>
+      <c r="GO71" s="1"/>
+      <c r="GP71" s="1"/>
+      <c r="GQ71" s="1"/>
+      <c r="GR71" s="1"/>
+      <c r="GS71" s="1"/>
+      <c r="GT71" s="1"/>
       <c r="GU71" s="1" t="s">
         <v>15</v>
       </c>
@@ -58434,6 +59097,17 @@
       <c r="FQ72" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ72" s="1"/>
+      <c r="GK72" s="1"/>
+      <c r="GL72" s="1"/>
+      <c r="GM72" s="1"/>
+      <c r="GN72" s="1"/>
+      <c r="GO72" s="1"/>
+      <c r="GP72" s="1"/>
+      <c r="GQ72" s="1"/>
+      <c r="GR72" s="1"/>
+      <c r="GS72" s="1"/>
+      <c r="GT72" s="1"/>
       <c r="GU72" s="1" t="s">
         <v>15</v>
       </c>
@@ -58640,6 +59314,17 @@
       <c r="FG73" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ73" s="1"/>
+      <c r="GK73" s="1"/>
+      <c r="GL73" s="1"/>
+      <c r="GM73" s="1"/>
+      <c r="GN73" s="1"/>
+      <c r="GO73" s="1"/>
+      <c r="GP73" s="1"/>
+      <c r="GQ73" s="1"/>
+      <c r="GR73" s="1"/>
+      <c r="GS73" s="1"/>
+      <c r="GT73" s="1"/>
       <c r="GU73" s="1" t="s">
         <v>15</v>
       </c>
@@ -58794,6 +59479,17 @@
       <c r="FM74" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ74" s="1"/>
+      <c r="GK74" s="1"/>
+      <c r="GL74" s="1"/>
+      <c r="GM74" s="1"/>
+      <c r="GN74" s="1"/>
+      <c r="GO74" s="1"/>
+      <c r="GP74" s="1"/>
+      <c r="GQ74" s="1"/>
+      <c r="GR74" s="1"/>
+      <c r="GS74" s="1"/>
+      <c r="GT74" s="1"/>
       <c r="GU74" s="1" t="s">
         <v>15</v>
       </c>
@@ -58965,6 +59661,17 @@
       <c r="FM75" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ75" s="1"/>
+      <c r="GK75" s="1"/>
+      <c r="GL75" s="1"/>
+      <c r="GM75" s="1"/>
+      <c r="GN75" s="1"/>
+      <c r="GO75" s="1"/>
+      <c r="GP75" s="1"/>
+      <c r="GQ75" s="1"/>
+      <c r="GR75" s="1"/>
+      <c r="GS75" s="1"/>
+      <c r="GT75" s="1"/>
       <c r="GU75" s="1" t="s">
         <v>15</v>
       </c>
@@ -59101,6 +59808,17 @@
       <c r="FI76" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ76" s="1"/>
+      <c r="GK76" s="1"/>
+      <c r="GL76" s="1"/>
+      <c r="GM76" s="1"/>
+      <c r="GN76" s="1"/>
+      <c r="GO76" s="1"/>
+      <c r="GP76" s="1"/>
+      <c r="GQ76" s="1"/>
+      <c r="GR76" s="1"/>
+      <c r="GS76" s="1"/>
+      <c r="GT76" s="1"/>
       <c r="GU76" s="1" t="s">
         <v>15</v>
       </c>
@@ -59366,6 +60084,17 @@
       <c r="FG77" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ77" s="1"/>
+      <c r="GK77" s="1"/>
+      <c r="GL77" s="1"/>
+      <c r="GM77" s="1"/>
+      <c r="GN77" s="1"/>
+      <c r="GO77" s="1"/>
+      <c r="GP77" s="1"/>
+      <c r="GQ77" s="1"/>
+      <c r="GR77" s="1"/>
+      <c r="GS77" s="1"/>
+      <c r="GT77" s="1"/>
       <c r="GU77" s="1" t="s">
         <v>15</v>
       </c>
@@ -59729,6 +60458,17 @@
       <c r="FG78" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ78" s="1"/>
+      <c r="GK78" s="1"/>
+      <c r="GL78" s="1"/>
+      <c r="GM78" s="1"/>
+      <c r="GN78" s="1"/>
+      <c r="GO78" s="1"/>
+      <c r="GP78" s="1"/>
+      <c r="GQ78" s="1"/>
+      <c r="GR78" s="1"/>
+      <c r="GS78" s="1"/>
+      <c r="GT78" s="1"/>
       <c r="GU78" s="1" t="s">
         <v>15</v>
       </c>
@@ -60075,6 +60815,17 @@
       <c r="FG79" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ79" s="1"/>
+      <c r="GK79" s="1"/>
+      <c r="GL79" s="1"/>
+      <c r="GM79" s="1"/>
+      <c r="GN79" s="1"/>
+      <c r="GO79" s="1"/>
+      <c r="GP79" s="1"/>
+      <c r="GQ79" s="1"/>
+      <c r="GR79" s="1"/>
+      <c r="GS79" s="1"/>
+      <c r="GT79" s="1"/>
       <c r="GU79" s="1" t="s">
         <v>15</v>
       </c>
@@ -60438,6 +61189,17 @@
       <c r="FG80" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ80" s="1"/>
+      <c r="GK80" s="1"/>
+      <c r="GL80" s="1"/>
+      <c r="GM80" s="1"/>
+      <c r="GN80" s="1"/>
+      <c r="GO80" s="1"/>
+      <c r="GP80" s="1"/>
+      <c r="GQ80" s="1"/>
+      <c r="GR80" s="1"/>
+      <c r="GS80" s="1"/>
+      <c r="GT80" s="1"/>
       <c r="GU80" s="1" t="s">
         <v>15</v>
       </c>
@@ -60616,6 +61378,17 @@
       <c r="FG81" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ81" s="1"/>
+      <c r="GK81" s="1"/>
+      <c r="GL81" s="1"/>
+      <c r="GM81" s="1"/>
+      <c r="GN81" s="1"/>
+      <c r="GO81" s="1"/>
+      <c r="GP81" s="1"/>
+      <c r="GQ81" s="1"/>
+      <c r="GR81" s="1"/>
+      <c r="GS81" s="1"/>
+      <c r="GT81" s="1"/>
       <c r="GU81" s="1" t="s">
         <v>15</v>
       </c>
@@ -60715,6 +61488,17 @@
       <c r="FG82" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ82" s="1"/>
+      <c r="GK82" s="1"/>
+      <c r="GL82" s="1"/>
+      <c r="GM82" s="1"/>
+      <c r="GN82" s="1"/>
+      <c r="GO82" s="1"/>
+      <c r="GP82" s="1"/>
+      <c r="GQ82" s="1"/>
+      <c r="GR82" s="1"/>
+      <c r="GS82" s="1"/>
+      <c r="GT82" s="1"/>
       <c r="GU82" s="1" t="s">
         <v>15</v>
       </c>
@@ -61087,6 +61871,17 @@
       <c r="FG84" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ84" s="1"/>
+      <c r="GK84" s="1"/>
+      <c r="GL84" s="1"/>
+      <c r="GM84" s="1"/>
+      <c r="GN84" s="1"/>
+      <c r="GO84" s="1"/>
+      <c r="GP84" s="1"/>
+      <c r="GQ84" s="1"/>
+      <c r="GR84" s="1"/>
+      <c r="GS84" s="1"/>
+      <c r="GT84" s="1"/>
       <c r="GU84" s="1" t="s">
         <v>15</v>
       </c>
@@ -61181,6 +61976,17 @@
       <c r="FG85" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ85" s="1"/>
+      <c r="GK85" s="1"/>
+      <c r="GL85" s="1"/>
+      <c r="GM85" s="1"/>
+      <c r="GN85" s="1"/>
+      <c r="GO85" s="1"/>
+      <c r="GP85" s="1"/>
+      <c r="GQ85" s="1"/>
+      <c r="GR85" s="1"/>
+      <c r="GS85" s="1"/>
+      <c r="GT85" s="1"/>
       <c r="GU85" s="1" t="s">
         <v>15</v>
       </c>
@@ -61290,6 +62096,17 @@
       <c r="FG86" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ86" s="1"/>
+      <c r="GK86" s="1"/>
+      <c r="GL86" s="1"/>
+      <c r="GM86" s="1"/>
+      <c r="GN86" s="1"/>
+      <c r="GO86" s="1"/>
+      <c r="GP86" s="1"/>
+      <c r="GQ86" s="1"/>
+      <c r="GR86" s="1"/>
+      <c r="GS86" s="1"/>
+      <c r="GT86" s="1"/>
       <c r="GU86" s="1" t="s">
         <v>15</v>
       </c>
@@ -61419,6 +62236,17 @@
       <c r="FG87" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ87" s="1"/>
+      <c r="GK87" s="1"/>
+      <c r="GL87" s="1"/>
+      <c r="GM87" s="1"/>
+      <c r="GN87" s="1"/>
+      <c r="GO87" s="1"/>
+      <c r="GP87" s="1"/>
+      <c r="GQ87" s="1"/>
+      <c r="GR87" s="1"/>
+      <c r="GS87" s="1"/>
+      <c r="GT87" s="1"/>
       <c r="GU87" s="1" t="s">
         <v>15</v>
       </c>
@@ -61548,6 +62376,17 @@
       <c r="FG88" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ88" s="1"/>
+      <c r="GK88" s="1"/>
+      <c r="GL88" s="1"/>
+      <c r="GM88" s="1"/>
+      <c r="GN88" s="1"/>
+      <c r="GO88" s="1"/>
+      <c r="GP88" s="1"/>
+      <c r="GQ88" s="1"/>
+      <c r="GR88" s="1"/>
+      <c r="GS88" s="1"/>
+      <c r="GT88" s="1"/>
       <c r="GU88" s="1" t="s">
         <v>15</v>
       </c>
@@ -61677,6 +62516,17 @@
       <c r="FG89" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ89" s="1"/>
+      <c r="GK89" s="1"/>
+      <c r="GL89" s="1"/>
+      <c r="GM89" s="1"/>
+      <c r="GN89" s="1"/>
+      <c r="GO89" s="1"/>
+      <c r="GP89" s="1"/>
+      <c r="GQ89" s="1"/>
+      <c r="GR89" s="1"/>
+      <c r="GS89" s="1"/>
+      <c r="GT89" s="1"/>
       <c r="GU89" s="1" t="s">
         <v>15</v>
       </c>
@@ -61803,6 +62653,17 @@
       <c r="FG90" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ90" s="1"/>
+      <c r="GK90" s="1"/>
+      <c r="GL90" s="1"/>
+      <c r="GM90" s="1"/>
+      <c r="GN90" s="1"/>
+      <c r="GO90" s="1"/>
+      <c r="GP90" s="1"/>
+      <c r="GQ90" s="1"/>
+      <c r="GR90" s="1"/>
+      <c r="GS90" s="1"/>
+      <c r="GT90" s="1"/>
       <c r="GU90" s="1" t="s">
         <v>15</v>
       </c>
@@ -61932,6 +62793,17 @@
       <c r="FG91" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ91" s="1"/>
+      <c r="GK91" s="1"/>
+      <c r="GL91" s="1"/>
+      <c r="GM91" s="1"/>
+      <c r="GN91" s="1"/>
+      <c r="GO91" s="1"/>
+      <c r="GP91" s="1"/>
+      <c r="GQ91" s="1"/>
+      <c r="GR91" s="1"/>
+      <c r="GS91" s="1"/>
+      <c r="GT91" s="1"/>
       <c r="GU91" s="1" t="s">
         <v>15</v>
       </c>
@@ -62061,6 +62933,17 @@
       <c r="FG92" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ92" s="1"/>
+      <c r="GK92" s="1"/>
+      <c r="GL92" s="1"/>
+      <c r="GM92" s="1"/>
+      <c r="GN92" s="1"/>
+      <c r="GO92" s="1"/>
+      <c r="GP92" s="1"/>
+      <c r="GQ92" s="1"/>
+      <c r="GR92" s="1"/>
+      <c r="GS92" s="1"/>
+      <c r="GT92" s="1"/>
       <c r="GU92" s="1" t="s">
         <v>15</v>
       </c>
@@ -62190,6 +63073,17 @@
       <c r="FG93" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ93" s="1"/>
+      <c r="GK93" s="1"/>
+      <c r="GL93" s="1"/>
+      <c r="GM93" s="1"/>
+      <c r="GN93" s="1"/>
+      <c r="GO93" s="1"/>
+      <c r="GP93" s="1"/>
+      <c r="GQ93" s="1"/>
+      <c r="GR93" s="1"/>
+      <c r="GS93" s="1"/>
+      <c r="GT93" s="1"/>
       <c r="GU93" s="1" t="s">
         <v>15</v>
       </c>
@@ -62307,6 +63201,17 @@
       <c r="FG94" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ94" s="1"/>
+      <c r="GK94" s="1"/>
+      <c r="GL94" s="1"/>
+      <c r="GM94" s="1"/>
+      <c r="GN94" s="1"/>
+      <c r="GO94" s="1"/>
+      <c r="GP94" s="1"/>
+      <c r="GQ94" s="1"/>
+      <c r="GR94" s="1"/>
+      <c r="GS94" s="1"/>
+      <c r="GT94" s="1"/>
       <c r="GU94" s="1" t="s">
         <v>15</v>
       </c>
@@ -62424,6 +63329,17 @@
       <c r="FG95" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ95" s="1"/>
+      <c r="GK95" s="1"/>
+      <c r="GL95" s="1"/>
+      <c r="GM95" s="1"/>
+      <c r="GN95" s="1"/>
+      <c r="GO95" s="1"/>
+      <c r="GP95" s="1"/>
+      <c r="GQ95" s="1"/>
+      <c r="GR95" s="1"/>
+      <c r="GS95" s="1"/>
+      <c r="GT95" s="1"/>
       <c r="GU95" s="1" t="s">
         <v>15</v>
       </c>
@@ -62541,6 +63457,17 @@
       <c r="FG96" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ96" s="1"/>
+      <c r="GK96" s="1"/>
+      <c r="GL96" s="1"/>
+      <c r="GM96" s="1"/>
+      <c r="GN96" s="1"/>
+      <c r="GO96" s="1"/>
+      <c r="GP96" s="1"/>
+      <c r="GQ96" s="1"/>
+      <c r="GR96" s="1"/>
+      <c r="GS96" s="1"/>
+      <c r="GT96" s="1"/>
       <c r="GU96" s="1" t="s">
         <v>15</v>
       </c>
@@ -62658,6 +63585,17 @@
       <c r="FG97" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ97" s="1"/>
+      <c r="GK97" s="1"/>
+      <c r="GL97" s="1"/>
+      <c r="GM97" s="1"/>
+      <c r="GN97" s="1"/>
+      <c r="GO97" s="1"/>
+      <c r="GP97" s="1"/>
+      <c r="GQ97" s="1"/>
+      <c r="GR97" s="1"/>
+      <c r="GS97" s="1"/>
+      <c r="GT97" s="1"/>
       <c r="GU97" s="1" t="s">
         <v>15</v>
       </c>
@@ -62775,6 +63713,17 @@
       <c r="FG98" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ98" s="1"/>
+      <c r="GK98" s="1"/>
+      <c r="GL98" s="1"/>
+      <c r="GM98" s="1"/>
+      <c r="GN98" s="1"/>
+      <c r="GO98" s="1"/>
+      <c r="GP98" s="1"/>
+      <c r="GQ98" s="1"/>
+      <c r="GR98" s="1"/>
+      <c r="GS98" s="1"/>
+      <c r="GT98" s="1"/>
       <c r="GU98" s="1" t="s">
         <v>15</v>
       </c>
@@ -62892,6 +63841,17 @@
       <c r="FG99" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ99" s="1"/>
+      <c r="GK99" s="1"/>
+      <c r="GL99" s="1"/>
+      <c r="GM99" s="1"/>
+      <c r="GN99" s="1"/>
+      <c r="GO99" s="1"/>
+      <c r="GP99" s="1"/>
+      <c r="GQ99" s="1"/>
+      <c r="GR99" s="1"/>
+      <c r="GS99" s="1"/>
+      <c r="GT99" s="1"/>
       <c r="GU99" s="1" t="s">
         <v>15</v>
       </c>
@@ -63009,6 +63969,17 @@
       <c r="FG100" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ100" s="1"/>
+      <c r="GK100" s="1"/>
+      <c r="GL100" s="1"/>
+      <c r="GM100" s="1"/>
+      <c r="GN100" s="1"/>
+      <c r="GO100" s="1"/>
+      <c r="GP100" s="1"/>
+      <c r="GQ100" s="1"/>
+      <c r="GR100" s="1"/>
+      <c r="GS100" s="1"/>
+      <c r="GT100" s="1"/>
       <c r="GU100" s="1" t="s">
         <v>15</v>
       </c>
@@ -63126,6 +64097,17 @@
       <c r="FG101" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ101" s="1"/>
+      <c r="GK101" s="1"/>
+      <c r="GL101" s="1"/>
+      <c r="GM101" s="1"/>
+      <c r="GN101" s="1"/>
+      <c r="GO101" s="1"/>
+      <c r="GP101" s="1"/>
+      <c r="GQ101" s="1"/>
+      <c r="GR101" s="1"/>
+      <c r="GS101" s="1"/>
+      <c r="GT101" s="1"/>
       <c r="GU101" s="1" t="s">
         <v>15</v>
       </c>
@@ -63240,6 +64222,17 @@
       <c r="FG102" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ102" s="1"/>
+      <c r="GK102" s="1"/>
+      <c r="GL102" s="1"/>
+      <c r="GM102" s="1"/>
+      <c r="GN102" s="1"/>
+      <c r="GO102" s="1"/>
+      <c r="GP102" s="1"/>
+      <c r="GQ102" s="1"/>
+      <c r="GR102" s="1"/>
+      <c r="GS102" s="1"/>
+      <c r="GT102" s="1"/>
       <c r="GU102" s="1" t="s">
         <v>15</v>
       </c>
@@ -63337,6 +64330,17 @@
       <c r="FG103" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ103" s="1"/>
+      <c r="GK103" s="1"/>
+      <c r="GL103" s="1"/>
+      <c r="GM103" s="1"/>
+      <c r="GN103" s="1"/>
+      <c r="GO103" s="1"/>
+      <c r="GP103" s="1"/>
+      <c r="GQ103" s="1"/>
+      <c r="GR103" s="1"/>
+      <c r="GS103" s="1"/>
+      <c r="GT103" s="1"/>
       <c r="GU103" s="1" t="s">
         <v>15</v>
       </c>
@@ -63434,6 +64438,17 @@
       <c r="FG104" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ104" s="1"/>
+      <c r="GK104" s="1"/>
+      <c r="GL104" s="1"/>
+      <c r="GM104" s="1"/>
+      <c r="GN104" s="1"/>
+      <c r="GO104" s="1"/>
+      <c r="GP104" s="1"/>
+      <c r="GQ104" s="1"/>
+      <c r="GR104" s="1"/>
+      <c r="GS104" s="1"/>
+      <c r="GT104" s="1"/>
       <c r="GU104" s="1" t="s">
         <v>15</v>
       </c>
@@ -63531,6 +64546,17 @@
       <c r="FG105" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ105" s="1"/>
+      <c r="GK105" s="1"/>
+      <c r="GL105" s="1"/>
+      <c r="GM105" s="1"/>
+      <c r="GN105" s="1"/>
+      <c r="GO105" s="1"/>
+      <c r="GP105" s="1"/>
+      <c r="GQ105" s="1"/>
+      <c r="GR105" s="1"/>
+      <c r="GS105" s="1"/>
+      <c r="GT105" s="1"/>
       <c r="GU105" s="1" t="s">
         <v>15</v>
       </c>
@@ -63628,6 +64654,17 @@
       <c r="FG106" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ106" s="1"/>
+      <c r="GK106" s="1"/>
+      <c r="GL106" s="1"/>
+      <c r="GM106" s="1"/>
+      <c r="GN106" s="1"/>
+      <c r="GO106" s="1"/>
+      <c r="GP106" s="1"/>
+      <c r="GQ106" s="1"/>
+      <c r="GR106" s="1"/>
+      <c r="GS106" s="1"/>
+      <c r="GT106" s="1"/>
       <c r="GU106" s="1" t="s">
         <v>15</v>
       </c>
@@ -63725,6 +64762,17 @@
       <c r="FG107" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ107" s="1"/>
+      <c r="GK107" s="1"/>
+      <c r="GL107" s="1"/>
+      <c r="GM107" s="1"/>
+      <c r="GN107" s="1"/>
+      <c r="GO107" s="1"/>
+      <c r="GP107" s="1"/>
+      <c r="GQ107" s="1"/>
+      <c r="GR107" s="1"/>
+      <c r="GS107" s="1"/>
+      <c r="GT107" s="1"/>
       <c r="GU107" s="1" t="s">
         <v>15</v>
       </c>
@@ -63822,6 +64870,17 @@
       <c r="FG108" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ108" s="1"/>
+      <c r="GK108" s="1"/>
+      <c r="GL108" s="1"/>
+      <c r="GM108" s="1"/>
+      <c r="GN108" s="1"/>
+      <c r="GO108" s="1"/>
+      <c r="GP108" s="1"/>
+      <c r="GQ108" s="1"/>
+      <c r="GR108" s="1"/>
+      <c r="GS108" s="1"/>
+      <c r="GT108" s="1"/>
       <c r="GU108" s="1" t="s">
         <v>15</v>
       </c>
@@ -63919,6 +64978,17 @@
       <c r="FG109" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ109" s="1"/>
+      <c r="GK109" s="1"/>
+      <c r="GL109" s="1"/>
+      <c r="GM109" s="1"/>
+      <c r="GN109" s="1"/>
+      <c r="GO109" s="1"/>
+      <c r="GP109" s="1"/>
+      <c r="GQ109" s="1"/>
+      <c r="GR109" s="1"/>
+      <c r="GS109" s="1"/>
+      <c r="GT109" s="1"/>
       <c r="GU109" s="1" t="s">
         <v>15</v>
       </c>
@@ -64016,6 +65086,17 @@
       <c r="FG110" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ110" s="1"/>
+      <c r="GK110" s="1"/>
+      <c r="GL110" s="1"/>
+      <c r="GM110" s="1"/>
+      <c r="GN110" s="1"/>
+      <c r="GO110" s="1"/>
+      <c r="GP110" s="1"/>
+      <c r="GQ110" s="1"/>
+      <c r="GR110" s="1"/>
+      <c r="GS110" s="1"/>
+      <c r="GT110" s="1"/>
       <c r="GU110" s="1" t="s">
         <v>15</v>
       </c>
@@ -64113,6 +65194,17 @@
       <c r="FG111" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ111" s="1"/>
+      <c r="GK111" s="1"/>
+      <c r="GL111" s="1"/>
+      <c r="GM111" s="1"/>
+      <c r="GN111" s="1"/>
+      <c r="GO111" s="1"/>
+      <c r="GP111" s="1"/>
+      <c r="GQ111" s="1"/>
+      <c r="GR111" s="1"/>
+      <c r="GS111" s="1"/>
+      <c r="GT111" s="1"/>
       <c r="GU111" s="1" t="s">
         <v>15</v>
       </c>
@@ -64210,6 +65302,17 @@
       <c r="FG112" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ112" s="1"/>
+      <c r="GK112" s="1"/>
+      <c r="GL112" s="1"/>
+      <c r="GM112" s="1"/>
+      <c r="GN112" s="1"/>
+      <c r="GO112" s="1"/>
+      <c r="GP112" s="1"/>
+      <c r="GQ112" s="1"/>
+      <c r="GR112" s="1"/>
+      <c r="GS112" s="1"/>
+      <c r="GT112" s="1"/>
       <c r="GU112" s="1" t="s">
         <v>15</v>
       </c>
@@ -64307,6 +65410,17 @@
       <c r="FG113" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ113" s="1"/>
+      <c r="GK113" s="1"/>
+      <c r="GL113" s="1"/>
+      <c r="GM113" s="1"/>
+      <c r="GN113" s="1"/>
+      <c r="GO113" s="1"/>
+      <c r="GP113" s="1"/>
+      <c r="GQ113" s="1"/>
+      <c r="GR113" s="1"/>
+      <c r="GS113" s="1"/>
+      <c r="GT113" s="1"/>
       <c r="GU113" s="1" t="s">
         <v>15</v>
       </c>
@@ -64404,6 +65518,17 @@
       <c r="FG114" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ114" s="1"/>
+      <c r="GK114" s="1"/>
+      <c r="GL114" s="1"/>
+      <c r="GM114" s="1"/>
+      <c r="GN114" s="1"/>
+      <c r="GO114" s="1"/>
+      <c r="GP114" s="1"/>
+      <c r="GQ114" s="1"/>
+      <c r="GR114" s="1"/>
+      <c r="GS114" s="1"/>
+      <c r="GT114" s="1"/>
       <c r="GU114" s="1" t="s">
         <v>15</v>
       </c>
@@ -64501,6 +65626,17 @@
       <c r="FG115" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ115" s="1"/>
+      <c r="GK115" s="1"/>
+      <c r="GL115" s="1"/>
+      <c r="GM115" s="1"/>
+      <c r="GN115" s="1"/>
+      <c r="GO115" s="1"/>
+      <c r="GP115" s="1"/>
+      <c r="GQ115" s="1"/>
+      <c r="GR115" s="1"/>
+      <c r="GS115" s="1"/>
+      <c r="GT115" s="1"/>
       <c r="GU115" s="1" t="s">
         <v>15</v>
       </c>
@@ -64613,6 +65749,17 @@
       <c r="FG116" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ116" s="1"/>
+      <c r="GK116" s="1"/>
+      <c r="GL116" s="1"/>
+      <c r="GM116" s="1"/>
+      <c r="GN116" s="1"/>
+      <c r="GO116" s="1"/>
+      <c r="GP116" s="1"/>
+      <c r="GQ116" s="1"/>
+      <c r="GR116" s="1"/>
+      <c r="GS116" s="1"/>
+      <c r="GT116" s="1"/>
       <c r="GU116" s="1" t="s">
         <v>15</v>
       </c>
@@ -64742,6 +65889,17 @@
       <c r="FG117" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ117" s="1"/>
+      <c r="GK117" s="1"/>
+      <c r="GL117" s="1"/>
+      <c r="GM117" s="1"/>
+      <c r="GN117" s="1"/>
+      <c r="GO117" s="1"/>
+      <c r="GP117" s="1"/>
+      <c r="GQ117" s="1"/>
+      <c r="GR117" s="1"/>
+      <c r="GS117" s="1"/>
+      <c r="GT117" s="1"/>
       <c r="GU117" s="1" t="s">
         <v>15</v>
       </c>
@@ -64871,6 +66029,17 @@
       <c r="FG118" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="GJ118" s="1"/>
+      <c r="GK118" s="1"/>
+      <c r="GL118" s="1"/>
+      <c r="GM118" s="1"/>
+      <c r="GN118" s="1"/>
+      <c r="GO118" s="1"/>
+      <c r="GP118" s="1"/>
+      <c r="GQ118" s="1"/>
+      <c r="GR118" s="1"/>
+      <c r="GS118" s="1"/>
+      <c r="GT118" s="1"/>
       <c r="GU118" s="1" t="s">
         <v>15</v>
       </c>
@@ -64970,6 +66139,17 @@
       <c r="JO118" s="1"/>
     </row>
     <row r="119">
+      <c r="GJ119" s="1"/>
+      <c r="GK119" s="1"/>
+      <c r="GL119" s="1"/>
+      <c r="GM119" s="1"/>
+      <c r="GN119" s="1"/>
+      <c r="GO119" s="1"/>
+      <c r="GP119" s="1"/>
+      <c r="GQ119" s="1"/>
+      <c r="GR119" s="1"/>
+      <c r="GS119" s="1"/>
+      <c r="GT119" s="1"/>
       <c r="HK119" s="1"/>
       <c r="HL119" s="1"/>
       <c r="HM119" s="1"/>

--- a/Master Lists.xlsx
+++ b/Master Lists.xlsx
@@ -38741,6 +38741,9 @@
       <c r="C8" s="2" t="s">
         <v>941</v>
       </c>
+      <c r="N8" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="FG8" s="1" t="s">
         <v>15</v>
       </c>
@@ -38846,6 +38849,9 @@
       <c r="C9" s="2" t="s">
         <v>941</v>
       </c>
+      <c r="N9" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="FG9" s="1" t="s">
         <v>15</v>
       </c>
@@ -39275,6 +39281,9 @@
       <c r="C13" s="2" t="s">
         <v>941</v>
       </c>
+      <c r="N13" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="FG13" s="1" t="s">
         <v>15</v>
       </c>
@@ -39380,6 +39389,9 @@
       <c r="C14" s="2" t="s">
         <v>941</v>
       </c>
+      <c r="N14" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="FG14" s="1" t="s">
         <v>15</v>
       </c>
@@ -39488,9 +39500,6 @@
       <c r="G15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="N15" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="FG15" s="1" t="s">
         <v>15</v>
       </c>
@@ -39599,9 +39608,6 @@
       <c r="G16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="N16" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="FG16" s="1" t="s">
         <v>15</v>
       </c>
@@ -39710,9 +39716,6 @@
       <c r="G17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="N17" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="FG17" s="1" t="s">
         <v>15</v>
       </c>
@@ -39845,6 +39848,9 @@
       <c r="CM18" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="CN18" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="CO18" s="1" t="s">
         <v>15</v>
       </c>
@@ -39857,6 +39863,9 @@
       <c r="CU18" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="CV18" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="CW18" s="1" t="s">
         <v>15</v>
       </c>
@@ -39869,6 +39878,9 @@
       <c r="DC18" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="DD18" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="DE18" s="1" t="s">
         <v>15</v>
       </c>
@@ -39881,6 +39893,9 @@
       <c r="DK18" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="DL18" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="DM18" s="1" t="s">
         <v>15</v>
       </c>
@@ -39893,6 +39908,9 @@
       <c r="DS18" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="DT18" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="DU18" s="1" t="s">
         <v>15</v>
       </c>
@@ -39903,6 +39921,9 @@
         <v>15</v>
       </c>
       <c r="EA18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="EB18" s="1" t="s">
         <v>15</v>
       </c>
       <c r="EC18" s="1" t="s">
@@ -40077,7 +40098,9 @@
       <c r="HJ18" s="1"/>
       <c r="HK18" s="1"/>
       <c r="HL18" s="1"/>
-      <c r="HM18" s="1"/>
+      <c r="HM18" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="HN18" s="1" t="s">
         <v>15</v>
       </c>
@@ -40096,7 +40119,9 @@
       <c r="HU18" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="HV18" s="1"/>
+      <c r="HV18" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="HW18" s="1" t="s">
         <v>15</v>
       </c>
@@ -40108,7 +40133,9 @@
       <c r="IA18" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="IB18" s="1"/>
+      <c r="IB18" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="IC18" s="1" t="s">
         <v>15</v>
       </c>
@@ -40389,6 +40416,9 @@
       <c r="CQ19" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="CR19" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="CS19" s="1" t="s">
         <v>15</v>
       </c>
@@ -40401,6 +40431,9 @@
       <c r="CY19" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="CZ19" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="DA19" s="1" t="s">
         <v>15</v>
       </c>
@@ -40413,6 +40446,9 @@
       <c r="DG19" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="DH19" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="DI19" s="1" t="s">
         <v>15</v>
       </c>
@@ -40425,6 +40461,9 @@
       <c r="DO19" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="DP19" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="DQ19" s="1" t="s">
         <v>15</v>
       </c>
@@ -40437,6 +40476,9 @@
       <c r="DW19" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="DX19" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="DY19" s="1" t="s">
         <v>15</v>
       </c>
@@ -40449,40 +40491,61 @@
       <c r="EE19" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="EF19" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="EG19" s="1" t="s">
         <v>15</v>
       </c>
       <c r="EJ19" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="EK19" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="EL19" s="1" t="s">
         <v>15</v>
       </c>
       <c r="EN19" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="EO19" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="EP19" s="1" t="s">
         <v>15</v>
       </c>
       <c r="ER19" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="ES19" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="ET19" s="1" t="s">
         <v>15</v>
       </c>
       <c r="EV19" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="EW19" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="EX19" s="1" t="s">
         <v>15</v>
       </c>
       <c r="EZ19" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="FA19" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="FB19" s="1" t="s">
         <v>15</v>
       </c>
       <c r="FD19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="FE19" s="1" t="s">
         <v>15</v>
       </c>
       <c r="FF19" s="1" t="s">
@@ -40663,7 +40726,9 @@
       <c r="HP19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="HQ19" s="1"/>
+      <c r="HQ19" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="HR19" s="1" t="s">
         <v>15</v>
       </c>
@@ -40678,7 +40743,9 @@
       <c r="HY19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="HZ19" s="1"/>
+      <c r="HZ19" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="IA19" s="1" t="s">
         <v>15</v>
       </c>
@@ -40690,7 +40757,9 @@
       <c r="IE19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="IF19" s="1"/>
+      <c r="IF19" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="IG19" s="1" t="s">
         <v>15</v>
       </c>
@@ -40698,7 +40767,9 @@
       <c r="II19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="IJ19" s="1"/>
+      <c r="IJ19" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="IK19" s="1" t="s">
         <v>15</v>
       </c>
@@ -40706,7 +40777,9 @@
       <c r="IM19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="IN19" s="1"/>
+      <c r="IN19" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="IO19" s="1" t="s">
         <v>15</v>
       </c>
@@ -40714,7 +40787,9 @@
       <c r="IQ19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="IR19" s="1"/>
+      <c r="IR19" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="IS19" s="1" t="s">
         <v>15</v>
       </c>
@@ -40722,7 +40797,9 @@
       <c r="IU19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="IV19" s="1"/>
+      <c r="IV19" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="IW19" s="1" t="s">
         <v>15</v>
       </c>
@@ -40730,7 +40807,9 @@
       <c r="IY19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="IZ19" s="1"/>
+      <c r="IZ19" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="JA19" s="1" t="s">
         <v>15</v>
       </c>
@@ -40738,7 +40817,9 @@
       <c r="JC19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="JD19" s="1"/>
+      <c r="JD19" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="JE19" s="1" t="s">
         <v>15</v>
       </c>
@@ -40746,7 +40827,9 @@
       <c r="JG19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="JH19" s="1"/>
+      <c r="JH19" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="JI19" s="1" t="s">
         <v>15</v>
       </c>
@@ -40754,7 +40837,9 @@
       <c r="JK19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="JL19" s="1"/>
+      <c r="JL19" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="JM19" s="1" t="s">
         <v>15</v>
       </c>
@@ -40804,39 +40889,16 @@
       <c r="FQ20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="GJ20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="GK20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="GL20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="GM20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="GN20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="GO20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="GP20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="GQ20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="GR20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="GS20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="GT20" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="GK20" s="1"/>
+      <c r="GL20" s="1"/>
+      <c r="GM20" s="1"/>
+      <c r="GN20" s="1"/>
+      <c r="GO20" s="1"/>
+      <c r="GP20" s="1"/>
+      <c r="GQ20" s="1"/>
+      <c r="GR20" s="1"/>
+      <c r="GS20" s="1"/>
+      <c r="GT20" s="1"/>
       <c r="GU20" s="1" t="s">
         <v>15</v>
       </c>
@@ -40882,9 +40944,7 @@
       <c r="HM20" s="1"/>
       <c r="HN20" s="1"/>
       <c r="HO20" s="1"/>
-      <c r="HP20" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="HP20" s="1"/>
       <c r="HQ20" s="1"/>
       <c r="HR20" s="1"/>
       <c r="HS20" s="1" t="s">
@@ -40897,65 +40957,45 @@
       <c r="HV20" s="1"/>
       <c r="HW20" s="1"/>
       <c r="HX20" s="1"/>
-      <c r="HY20" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="HY20" s="1"/>
       <c r="HZ20" s="1"/>
       <c r="IA20" s="1"/>
       <c r="IB20" s="1"/>
       <c r="IC20" s="1"/>
       <c r="ID20" s="1"/>
-      <c r="IE20" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="IE20" s="1"/>
       <c r="IF20" s="1"/>
       <c r="IG20" s="1"/>
       <c r="IH20" s="1"/>
-      <c r="II20" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="II20" s="1"/>
       <c r="IJ20" s="1"/>
       <c r="IK20" s="1"/>
       <c r="IL20" s="1"/>
-      <c r="IM20" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="IM20" s="1"/>
       <c r="IN20" s="1"/>
       <c r="IO20" s="1"/>
       <c r="IP20" s="1"/>
-      <c r="IQ20" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="IQ20" s="1"/>
       <c r="IR20" s="1"/>
       <c r="IS20" s="1"/>
       <c r="IT20" s="1"/>
-      <c r="IU20" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="IU20" s="1"/>
       <c r="IV20" s="1"/>
       <c r="IW20" s="1"/>
       <c r="IX20" s="1"/>
-      <c r="IY20" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="IY20" s="1"/>
       <c r="IZ20" s="1"/>
       <c r="JA20" s="1"/>
       <c r="JB20" s="1"/>
-      <c r="JC20" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="JC20" s="1"/>
       <c r="JD20" s="1"/>
       <c r="JE20" s="1"/>
       <c r="JF20" s="1"/>
-      <c r="JG20" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="JG20" s="1"/>
       <c r="JH20" s="1"/>
       <c r="JI20" s="1"/>
       <c r="JJ20" s="1"/>
-      <c r="JK20" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="JK20" s="1"/>
       <c r="JL20" s="1"/>
       <c r="JM20" s="1"/>
       <c r="JN20" s="1"/>
@@ -41600,60 +41640,168 @@
       <c r="CM22" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="CN22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="CO22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="CQ22" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="CR22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="CS22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="CU22" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="CV22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="CW22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="CY22" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="CZ22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="DA22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="DC22" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="DD22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="DE22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="DG22" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="DH22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="DI22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="DK22" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="DL22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="DM22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="DO22" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="DP22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="DQ22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="DS22" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="DT22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="DU22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="DW22" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="DX22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="DY22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="EA22" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="EB22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="EC22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="EE22" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="EF22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="EG22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="EH22" s="1" t="s">
         <v>15</v>
       </c>
       <c r="EJ22" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="EK22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="EL22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="EN22" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="EO22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="EP22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="ER22" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="ES22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="ET22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="EV22" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="EW22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="EX22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="EZ22" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="FA22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="FB22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="FD22" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="FE22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="FF22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="FG22" s="1" t="s">
         <v>15</v>
       </c>
@@ -41819,14 +41967,22 @@
       <c r="HL22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="HM22" s="1"/>
-      <c r="HN22" s="1"/>
+      <c r="HM22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="HN22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="HO22" s="1"/>
       <c r="HP22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="HQ22" s="1"/>
-      <c r="HR22" s="1"/>
+      <c r="HQ22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="HR22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="HS22" s="1" t="s">
         <v>15</v>
       </c>
@@ -41834,70 +41990,118 @@
       <c r="HU22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="HV22" s="1"/>
-      <c r="HW22" s="1"/>
+      <c r="HV22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="HW22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="HX22" s="1"/>
       <c r="HY22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="HZ22" s="1"/>
-      <c r="IA22" s="1"/>
-      <c r="IB22" s="1"/>
-      <c r="IC22" s="1"/>
+      <c r="HZ22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="IA22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="IB22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="IC22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="ID22" s="1"/>
       <c r="IE22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="IF22" s="1"/>
-      <c r="IG22" s="1"/>
+      <c r="IF22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="IG22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="IH22" s="1"/>
       <c r="II22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="IJ22" s="1"/>
-      <c r="IK22" s="1"/>
+      <c r="IJ22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="IK22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="IL22" s="1"/>
       <c r="IM22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="IN22" s="1"/>
-      <c r="IO22" s="1"/>
+      <c r="IN22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="IO22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="IP22" s="1"/>
       <c r="IQ22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="IR22" s="1"/>
-      <c r="IS22" s="1"/>
+      <c r="IR22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="IS22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="IT22" s="1"/>
       <c r="IU22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="IV22" s="1"/>
-      <c r="IW22" s="1"/>
+      <c r="IV22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="IW22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="IX22" s="1"/>
       <c r="IY22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="IZ22" s="1"/>
-      <c r="JA22" s="1"/>
+      <c r="IZ22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="JA22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="JB22" s="1"/>
       <c r="JC22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="JD22" s="1"/>
-      <c r="JE22" s="1"/>
+      <c r="JD22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="JE22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="JF22" s="1"/>
       <c r="JG22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="JH22" s="1"/>
-      <c r="JI22" s="1"/>
+      <c r="JH22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="JI22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="JJ22" s="1"/>
       <c r="JK22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="JL22" s="1"/>
-      <c r="JM22" s="1"/>
+      <c r="JL22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="JM22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="JN22" s="1"/>
       <c r="JO22" s="1"/>
     </row>
@@ -41992,108 +42196,162 @@
       <c r="CM23" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="CN23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="CO23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="CQ23" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="CR23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="CS23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="CU23" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="CV23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="CW23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="CY23" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="CZ23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="DA23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="DC23" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="DD23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="DE23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="DG23" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="DH23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="DI23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="DK23" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="DL23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="DM23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="DO23" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="DP23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="DQ23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="DS23" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="DT23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="DU23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="DW23" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="DX23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="DY23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="EA23" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="EB23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="EC23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="EE23" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="EF23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="EG23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="EJ23" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="EK23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="EL23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="EN23" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="EO23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="EP23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="ER23" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="ES23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="ET23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="EV23" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="EW23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="EX23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="EZ23" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="FA23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="FB23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="FD23" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="FE23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="FF23" s="1" t="s">
         <v>15</v>
       </c>
@@ -42181,17 +42439,39 @@
       <c r="GI23" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="GJ23" s="1"/>
-      <c r="GK23" s="1"/>
-      <c r="GL23" s="1"/>
-      <c r="GM23" s="1"/>
-      <c r="GN23" s="1"/>
-      <c r="GO23" s="1"/>
-      <c r="GP23" s="1"/>
-      <c r="GQ23" s="1"/>
-      <c r="GR23" s="1"/>
-      <c r="GS23" s="1"/>
-      <c r="GT23" s="1"/>
+      <c r="GJ23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="GK23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="GL23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="GM23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="GN23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="GO23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="GP23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="GQ23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="GR23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="GS23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="GT23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="GU23" s="1" t="s">
         <v>15</v>
       </c>
@@ -42237,13 +42517,19 @@
       <c r="HJ23" s="1"/>
       <c r="HK23" s="1"/>
       <c r="HL23" s="1"/>
-      <c r="HM23" s="1"/>
+      <c r="HM23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="HN23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="HO23" s="1"/>
-      <c r="HP23" s="1"/>
-      <c r="HQ23" s="1"/>
+      <c r="HP23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="HQ23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="HR23" s="1" t="s">
         <v>15</v>
       </c>
@@ -42254,71 +42540,115 @@
       <c r="HU23" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="HV23" s="1"/>
+      <c r="HV23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="HW23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="HX23" s="1"/>
-      <c r="HY23" s="1"/>
-      <c r="HZ23" s="1"/>
+      <c r="HY23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="HZ23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="IA23" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="IB23" s="1"/>
+      <c r="IB23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="IC23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="ID23" s="1"/>
-      <c r="IE23" s="1"/>
-      <c r="IF23" s="1"/>
+      <c r="IE23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="IF23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="IG23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="IH23" s="1"/>
-      <c r="II23" s="1"/>
-      <c r="IJ23" s="1"/>
+      <c r="II23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="IJ23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="IK23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="IL23" s="1"/>
-      <c r="IM23" s="1"/>
-      <c r="IN23" s="1"/>
+      <c r="IM23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="IN23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="IO23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="IP23" s="1"/>
-      <c r="IQ23" s="1"/>
-      <c r="IR23" s="1"/>
+      <c r="IQ23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="IR23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="IS23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="IT23" s="1"/>
-      <c r="IU23" s="1"/>
-      <c r="IV23" s="1"/>
+      <c r="IU23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="IV23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="IW23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="IX23" s="1"/>
-      <c r="IY23" s="1"/>
-      <c r="IZ23" s="1"/>
+      <c r="IY23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="IZ23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="JA23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="JB23" s="1"/>
-      <c r="JC23" s="1"/>
-      <c r="JD23" s="1"/>
+      <c r="JC23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="JD23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="JE23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="JF23" s="1"/>
-      <c r="JG23" s="1"/>
-      <c r="JH23" s="1"/>
+      <c r="JG23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="JH23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="JI23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="JJ23" s="1"/>
-      <c r="JK23" s="1"/>
-      <c r="JL23" s="1"/>
+      <c r="JK23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="JL23" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="JM23" s="1" t="s">
         <v>15</v>
       </c>
@@ -42366,6 +42696,9 @@
         <v>15</v>
       </c>
       <c r="Y24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD24" s="1" t="s">
         <v>15</v>
       </c>
       <c r="AI24" s="1" t="s">
@@ -42530,9 +42863,6 @@
       <c r="C25" s="2" t="s">
         <v>958</v>
       </c>
-      <c r="AD25" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="BP25" s="1" t="s">
         <v>15</v>
       </c>
@@ -46302,6 +46632,12 @@
       <c r="C46" s="2" t="s">
         <v>985</v>
       </c>
+      <c r="D46" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z46" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="AT46" s="1" t="s">
         <v>15</v>
       </c>
@@ -49227,6 +49563,12 @@
       <c r="C52" s="2" t="s">
         <v>985</v>
       </c>
+      <c r="D52" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z52" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="AT52" s="1" t="s">
         <v>15</v>
       </c>
@@ -52176,6 +52518,12 @@
       <c r="I58" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="K58" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z58" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="AT58" s="1" t="s">
         <v>15</v>
       </c>
@@ -53162,12 +53510,6 @@
       <c r="C60" s="2" t="s">
         <v>985</v>
       </c>
-      <c r="H60" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I60" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="Q60" s="1" t="s">
         <v>15</v>
       </c>
@@ -54154,12 +54496,6 @@
       <c r="C62" s="2" t="s">
         <v>985</v>
       </c>
-      <c r="H62" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="Q62" s="1" t="s">
         <v>15</v>
       </c>
@@ -54665,12 +55001,6 @@
       <c r="C63" s="2" t="s">
         <v>985</v>
       </c>
-      <c r="H63" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="AV63" s="1" t="s">
         <v>15</v>
       </c>
@@ -55125,6 +55455,12 @@
       <c r="I64" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="K64" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z64" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="AT64" s="1" t="s">
         <v>15</v>
       </c>
@@ -57060,6 +57396,12 @@
       </c>
       <c r="C68" s="2" t="s">
         <v>1010</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="Z68" s="1" t="s">
         <v>15</v>
@@ -63704,6 +64046,12 @@
       <c r="C98" s="2" t="s">
         <v>1031</v>
       </c>
+      <c r="H98" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="AP98" s="1" t="s">
         <v>15</v>
       </c>
@@ -63832,6 +64180,12 @@
       <c r="C99" s="2" t="s">
         <v>1031</v>
       </c>
+      <c r="H99" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="AP99" s="1" t="s">
         <v>15</v>
       </c>
@@ -63960,6 +64314,12 @@
       <c r="C100" s="2" t="s">
         <v>1031</v>
       </c>
+      <c r="H100" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="AP100" s="1" t="s">
         <v>15</v>
       </c>
@@ -64087,6 +64447,12 @@
       </c>
       <c r="C101" s="2" t="s">
         <v>1031</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="AP101" s="1" t="s">
         <v>15</v>

--- a/Master Lists.xlsx
+++ b/Master Lists.xlsx
@@ -43526,6 +43526,9 @@
       <c r="C31" s="2" t="s">
         <v>967</v>
       </c>
+      <c r="AR31" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="FG31" s="1" t="s">
         <v>15</v>
       </c>
@@ -56925,6 +56928,9 @@
       <c r="BI67" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="BK67" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="BO67" s="1" t="s">
         <v>15</v>
       </c>
@@ -56961,7 +56967,22 @@
       <c r="CD67" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="CE67" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="CF67" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="CG67" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="CH67" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="CI67" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="CJ67" s="1" t="s">
         <v>15</v>
       </c>
       <c r="CL67" s="1" t="s">
@@ -57439,6 +57460,9 @@
       <c r="BH68" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="BK68" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="BO68" s="1" t="s">
         <v>15</v>
       </c>
@@ -57451,7 +57475,22 @@
       <c r="CD68" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="CE68" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="CF68" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="CG68" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="CH68" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="CI68" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="CJ68" s="1" t="s">
         <v>15</v>
       </c>
       <c r="CL68" s="1" t="s">
@@ -57890,6 +57929,9 @@
       <c r="BI69" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="BK69" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="BO69" s="1" t="s">
         <v>15</v>
       </c>
@@ -57920,7 +57962,22 @@
       <c r="CD69" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="CE69" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="CF69" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="CG69" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="CH69" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="CI69" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="CJ69" s="1" t="s">
         <v>15</v>
       </c>
       <c r="CK69" s="1" t="s">
@@ -58357,6 +58414,9 @@
       <c r="BI70" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="BK70" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="BO70" s="1" t="s">
         <v>15</v>
       </c>
@@ -58387,7 +58447,22 @@
       <c r="CD70" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="CE70" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="CF70" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="CG70" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="CH70" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="CI70" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="CJ70" s="1" t="s">
         <v>15</v>
       </c>
       <c r="CK70" s="1" t="s">
@@ -58827,6 +58902,9 @@
       <c r="BI71" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="BK71" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="BO71" s="1" t="s">
         <v>15</v>
       </c>
@@ -59239,6 +59317,9 @@
         <v>15</v>
       </c>
       <c r="BE72" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="BK72" s="1" t="s">
         <v>15</v>
       </c>
       <c r="BO72" s="1" t="s">

--- a/Master Lists.xlsx
+++ b/Master Lists.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="7" activeTab="8"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="7" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Item Master" sheetId="1" r:id="rId1"/>
@@ -6806,7 +6806,7 @@
         <v>85</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>14</v>
@@ -20075,7 +20075,7 @@
         <v>178</v>
       </c>
       <c r="D2" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>179</v>
@@ -20101,7 +20101,7 @@
         <v>182</v>
       </c>
       <c r="D3" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>179</v>
@@ -20127,7 +20127,7 @@
         <v>184</v>
       </c>
       <c r="D4" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>179</v>
@@ -20153,7 +20153,7 @@
         <v>178</v>
       </c>
       <c r="D5" s="1">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>179</v>
@@ -20179,7 +20179,7 @@
         <v>182</v>
       </c>
       <c r="D6" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>179</v>
@@ -20205,7 +20205,7 @@
         <v>190</v>
       </c>
       <c r="D7" s="1">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>179</v>
@@ -20231,7 +20231,7 @@
         <v>184</v>
       </c>
       <c r="D8" s="1">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>179</v>
@@ -20257,7 +20257,7 @@
         <v>192</v>
       </c>
       <c r="D9" s="1">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>179</v>
@@ -20283,7 +20283,7 @@
         <v>192</v>
       </c>
       <c r="D10" s="1">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>179</v>
@@ -20309,7 +20309,7 @@
         <v>178</v>
       </c>
       <c r="D11" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>179</v>
@@ -20335,7 +20335,7 @@
         <v>182</v>
       </c>
       <c r="D12" s="1">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>179</v>
@@ -20361,7 +20361,7 @@
         <v>190</v>
       </c>
       <c r="D13" s="1">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>179</v>
@@ -20387,7 +20387,7 @@
         <v>182</v>
       </c>
       <c r="D14" s="1">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>179</v>
@@ -20413,7 +20413,7 @@
         <v>182</v>
       </c>
       <c r="D15" s="1">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>179</v>
@@ -20439,7 +20439,7 @@
         <v>190</v>
       </c>
       <c r="D16" s="1">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>179</v>
@@ -20465,7 +20465,7 @@
         <v>182</v>
       </c>
       <c r="D17" s="1">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>179</v>
@@ -20491,7 +20491,7 @@
         <v>192</v>
       </c>
       <c r="D18" s="1">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>179</v>
@@ -20517,7 +20517,7 @@
         <v>178</v>
       </c>
       <c r="D19" s="1">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>179</v>
@@ -20543,7 +20543,7 @@
         <v>178</v>
       </c>
       <c r="D20" s="1">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>179</v>
@@ -20569,7 +20569,7 @@
         <v>178</v>
       </c>
       <c r="D21" s="1">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>179</v>
@@ -20595,7 +20595,7 @@
         <v>178</v>
       </c>
       <c r="D22" s="1">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>179</v>
@@ -20621,7 +20621,7 @@
         <v>178</v>
       </c>
       <c r="D23" s="1">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>179</v>
@@ -20647,7 +20647,7 @@
         <v>182</v>
       </c>
       <c r="D24" s="1">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>179</v>
@@ -20673,7 +20673,7 @@
         <v>178</v>
       </c>
       <c r="D25" s="1">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>179</v>
@@ -20699,7 +20699,7 @@
         <v>178</v>
       </c>
       <c r="D26" s="1">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>179</v>
@@ -20725,7 +20725,7 @@
         <v>178</v>
       </c>
       <c r="D27" s="1">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>179</v>
@@ -20751,7 +20751,7 @@
         <v>182</v>
       </c>
       <c r="D28" s="1">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>179</v>
@@ -20777,7 +20777,7 @@
         <v>192</v>
       </c>
       <c r="D29" s="1">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>179</v>
@@ -20803,7 +20803,7 @@
         <v>184</v>
       </c>
       <c r="D30" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>225</v>
@@ -20829,7 +20829,7 @@
         <v>89</v>
       </c>
       <c r="D31" s="1">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>225</v>
@@ -20855,7 +20855,7 @@
         <v>184</v>
       </c>
       <c r="D32" s="1">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>225</v>
@@ -20881,7 +20881,7 @@
         <v>184</v>
       </c>
       <c r="D33" s="1">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>225</v>
@@ -20907,7 +20907,7 @@
         <v>178</v>
       </c>
       <c r="D34" s="1">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>225</v>
@@ -20933,7 +20933,7 @@
         <v>184</v>
       </c>
       <c r="D35" s="1">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>225</v>
@@ -20959,7 +20959,7 @@
         <v>184</v>
       </c>
       <c r="D36" s="1">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>225</v>
@@ -20985,7 +20985,7 @@
         <v>184</v>
       </c>
       <c r="D37" s="1">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>225</v>
@@ -21011,7 +21011,7 @@
         <v>184</v>
       </c>
       <c r="D38" s="1">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>225</v>
@@ -21037,7 +21037,7 @@
         <v>184</v>
       </c>
       <c r="D39" s="1">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>225</v>
@@ -21089,7 +21089,7 @@
         <v>184</v>
       </c>
       <c r="D41" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>225</v>
@@ -21115,7 +21115,7 @@
         <v>184</v>
       </c>
       <c r="D42" s="1">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>225</v>
@@ -21141,7 +21141,7 @@
         <v>184</v>
       </c>
       <c r="D43" s="1">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>225</v>
@@ -21167,7 +21167,7 @@
         <v>184</v>
       </c>
       <c r="D44" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>225</v>
@@ -21219,7 +21219,7 @@
         <v>184</v>
       </c>
       <c r="D46" s="1">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>225</v>
@@ -21245,7 +21245,7 @@
         <v>184</v>
       </c>
       <c r="D47" s="1">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>225</v>
@@ -21271,7 +21271,7 @@
         <v>184</v>
       </c>
       <c r="D48" s="1">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>225</v>
@@ -21297,7 +21297,7 @@
         <v>184</v>
       </c>
       <c r="D49" s="1">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>225</v>
@@ -21323,7 +21323,7 @@
         <v>182</v>
       </c>
       <c r="D50" s="1">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>239</v>
@@ -21349,7 +21349,7 @@
         <v>65</v>
       </c>
       <c r="D51" s="1">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>239</v>
@@ -21375,7 +21375,7 @@
         <v>182</v>
       </c>
       <c r="D52" s="1">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>239</v>
@@ -21401,7 +21401,7 @@
         <v>182</v>
       </c>
       <c r="D53" s="1">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>239</v>
@@ -21427,7 +21427,7 @@
         <v>182</v>
       </c>
       <c r="D54" s="1">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>239</v>
@@ -21453,7 +21453,7 @@
         <v>249</v>
       </c>
       <c r="D55" s="1">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>239</v>
@@ -21479,7 +21479,7 @@
         <v>251</v>
       </c>
       <c r="D56" s="1">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>239</v>
@@ -21505,7 +21505,7 @@
         <v>182</v>
       </c>
       <c r="D57" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>239</v>
@@ -21531,7 +21531,7 @@
         <v>58</v>
       </c>
       <c r="D58" s="1">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>239</v>
@@ -21557,7 +21557,7 @@
         <v>182</v>
       </c>
       <c r="D59" s="1">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>239</v>
@@ -21583,7 +21583,7 @@
         <v>65</v>
       </c>
       <c r="D60" s="1">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>239</v>
@@ -21609,7 +21609,7 @@
         <v>251</v>
       </c>
       <c r="D61" s="1">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>239</v>
@@ -21635,7 +21635,7 @@
         <v>182</v>
       </c>
       <c r="D62" s="1">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>239</v>
@@ -21661,7 +21661,7 @@
         <v>251</v>
       </c>
       <c r="D63" s="1">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>239</v>

--- a/Master Lists.xlsx
+++ b/Master Lists.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="7" activeTab="2"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="7" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Item Master" sheetId="1" r:id="rId1"/>
@@ -3706,13 +3706,13 @@
     <t>Fever Facility</t>
   </si>
   <si>
+    <t>L1 ED</t>
+  </si>
+  <si>
     <t>ED X-Ray</t>
   </si>
   <si>
     <t>Room 1</t>
-  </si>
-  <si>
-    <t>L1 ED</t>
   </si>
   <si>
     <t>Room 2</t>
@@ -10112,8 +10112,12 @@
       <c r="E50" s="1" t="s">
         <v>1165</v>
       </c>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
+      <c r="F50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>1225</v>
+      </c>
       <c r="H50" s="1" t="s">
         <v>15</v>
       </c>
@@ -10135,16 +10139,16 @@
         <v>1118</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>1226</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>1227</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G51" s="1" t="s">
         <v>1225</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>1226</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>1227</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>15</v>
@@ -10167,7 +10171,7 @@
         <v>1118</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>1228</v>
@@ -10176,7 +10180,7 @@
         <v>15</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>15</v>
@@ -10199,7 +10203,7 @@
         <v>1118</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>1120</v>
@@ -10208,7 +10212,7 @@
         <v>15</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>15</v>
@@ -10231,7 +10235,7 @@
         <v>1118</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>1229</v>

--- a/Master Lists.xlsx
+++ b/Master Lists.xlsx
@@ -3565,7 +3565,7 @@
     <t>Orthopaedic Therapy</t>
   </si>
   <si>
-    <t>L5 A52 Orthopaedic Equip Rm</t>
+    <t>L5 A52 Orthopaedic Therapy Rm</t>
   </si>
   <si>
     <t>A54 ENT</t>
